--- a/data/temp(중국).xlsx
+++ b/data/temp(중국).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\최봉수\Desktop\계획수립\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F8D80F-5C65-4B06-971B-6152B4580149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F88643-1B1F-4FDB-8FE4-B73CB56B7B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" tabRatio="613" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="748">
   <si>
     <t xml:space="preserve"> APBL2-AL22 G</t>
   </si>
@@ -681,9 +681,6 @@
     <t>016532</t>
   </si>
   <si>
-    <t>T.T.R</t>
-  </si>
-  <si>
     <t>6P(일체형)</t>
   </si>
   <si>
@@ -937,9 +934,6 @@
   </si>
   <si>
     <t>019846</t>
-  </si>
-  <si>
-    <t>021738</t>
   </si>
   <si>
     <t>014906</t>
@@ -1658,9 +1652,6 @@
   </si>
   <si>
     <t>(RE SET)AC 220V ASS`Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> V형 M S/W 유동접점콕킹 ASS'Y</t>
   </si>
   <si>
     <t>YSSK MY-2S(RY08A-C6)</t>
@@ -1862,21 +1853,6 @@
   </si>
   <si>
     <t>028585</t>
-  </si>
-  <si>
-    <t>028758</t>
-  </si>
-  <si>
-    <t>028759</t>
-  </si>
-  <si>
-    <t>028760</t>
-  </si>
-  <si>
-    <t>028761</t>
-  </si>
-  <si>
-    <t>028762</t>
   </si>
   <si>
     <t>11&amp;12차
@@ -2085,21 +2061,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>소형 리미트 고정점점콕킹 ASSY(단-좌)</t>
-  </si>
-  <si>
-    <t>소형 리미트 고정점점콕킹 ASSY(단-우)</t>
-  </si>
-  <si>
-    <t>소형 리미트 고정점점콕킹 ASSY(장-좌)</t>
-  </si>
-  <si>
-    <t>소형 리미트 고정점점콕킹 ASSY(장-우)</t>
-  </si>
-  <si>
-    <t>소형 리미트 유동접점 콕킹 ASS`Y</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Z형 M S/W 1번고정접점콕킹 ASS'Y</t>
   </si>
   <si>
@@ -2125,19 +2086,11 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>리미트</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>모자이크 5A</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>5A CAM</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPBL</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -2414,6 +2367,48 @@
   </si>
   <si>
     <t>007450</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPBL</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>리미트</t>
+  </si>
+  <si>
+    <t>B형</t>
+  </si>
+  <si>
+    <t>033595</t>
+  </si>
+  <si>
+    <t>BR2 2단 K형 홀다 ASS'Y</t>
+  </si>
+  <si>
+    <t>033594</t>
+  </si>
+  <si>
+    <t>BP1 25@ 홀다 ASS'Y B</t>
+  </si>
+  <si>
+    <t>033593</t>
+  </si>
+  <si>
+    <t>BP1 25@ 홀다 ASS'Y R</t>
+  </si>
+  <si>
+    <t>033592</t>
+  </si>
+  <si>
+    <t>BPBL 25@ 홀다 ASS'Y G</t>
+  </si>
+  <si>
+    <t>NPBL 고정접점(NC) ASS`Y A</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPBL 고정접점(NC) ASS`Y B</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2521,7 +2516,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -2958,6 +2953,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2976,7 +2982,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3127,6 +3133,12 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3136,28 +3148,58 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3199,73 +3241,58 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6252,20 +6279,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="80"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30"/>
@@ -6281,13 +6308,13 @@
       <c r="K3" s="30"/>
       <c r="L3" s="30"/>
       <c r="M3" s="31" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="N3" s="49"/>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M4" s="36" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="N4" s="49"/>
     </row>
@@ -6296,67 +6323,67 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88" t="s">
-        <v>414</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>624</v>
-      </c>
-      <c r="C6" s="83" t="s">
-        <v>625</v>
-      </c>
-      <c r="D6" s="83" t="s">
-        <v>626</v>
-      </c>
-      <c r="E6" s="83" t="s">
-        <v>627</v>
-      </c>
-      <c r="F6" s="78" t="s">
-        <v>628</v>
-      </c>
-      <c r="G6" s="78" t="s">
-        <v>578</v>
-      </c>
-      <c r="H6" s="78" t="s">
-        <v>582</v>
-      </c>
-      <c r="I6" s="78" t="s">
-        <v>588</v>
-      </c>
-      <c r="J6" s="78" t="s">
-        <v>589</v>
-      </c>
-      <c r="K6" s="78" t="s">
-        <v>590</v>
-      </c>
-      <c r="L6" s="78" t="s">
-        <v>608</v>
-      </c>
-      <c r="M6" s="78" t="s">
-        <v>629</v>
-      </c>
-      <c r="N6" s="81" t="s">
-        <v>630</v>
+      <c r="A6" s="64" t="s">
+        <v>412</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>616</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>617</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>618</v>
+      </c>
+      <c r="E6" s="59" t="s">
+        <v>619</v>
+      </c>
+      <c r="F6" s="55" t="s">
+        <v>620</v>
+      </c>
+      <c r="G6" s="55" t="s">
+        <v>575</v>
+      </c>
+      <c r="H6" s="55" t="s">
+        <v>579</v>
+      </c>
+      <c r="I6" s="55" t="s">
+        <v>585</v>
+      </c>
+      <c r="J6" s="55" t="s">
+        <v>586</v>
+      </c>
+      <c r="K6" s="55" t="s">
+        <v>587</v>
+      </c>
+      <c r="L6" s="55" t="s">
+        <v>600</v>
+      </c>
+      <c r="M6" s="55" t="s">
+        <v>621</v>
+      </c>
+      <c r="N6" s="71" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="89"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="84"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="79"/>
-      <c r="K7" s="79"/>
-      <c r="L7" s="79"/>
-      <c r="M7" s="79"/>
-      <c r="N7" s="82"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="72"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="87" t="s">
+      <c r="A8" s="61" t="s">
         <v>150</v>
       </c>
       <c r="B8" s="22" t="s">
@@ -6378,7 +6405,7 @@
       <c r="N8" s="24"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="59"/>
+      <c r="A9" s="62"/>
       <c r="B9" s="15" t="s">
         <v>186</v>
       </c>
@@ -6398,9 +6425,9 @@
       <c r="N9" s="14"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="59"/>
+      <c r="A10" s="62"/>
       <c r="B10" s="15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>144</v>
@@ -6418,9 +6445,9 @@
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="59"/>
+      <c r="A11" s="62"/>
       <c r="B11" s="15" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>139</v>
@@ -6438,9 +6465,9 @@
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="59"/>
+      <c r="A12" s="62"/>
       <c r="B12" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>152</v>
@@ -6458,9 +6485,9 @@
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59"/>
+      <c r="A13" s="62"/>
       <c r="B13" s="15" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>151</v>
@@ -6478,7 +6505,7 @@
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="59"/>
+      <c r="A14" s="62"/>
       <c r="B14" s="15" t="s">
         <v>193</v>
       </c>
@@ -6498,9 +6525,9 @@
       <c r="N14" s="14"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="59"/>
+      <c r="A15" s="62"/>
       <c r="B15" s="15" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>166</v>
@@ -6518,14 +6545,14 @@
       <c r="N15" s="14"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="50" t="s">
+      <c r="A16" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="52"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="54"/>
       <c r="G16" s="37"/>
       <c r="H16" s="37"/>
       <c r="I16" s="37"/>
@@ -6536,8 +6563,8 @@
       <c r="N16" s="14"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="60" t="s">
-        <v>634</v>
+      <c r="A17" s="63" t="s">
+        <v>626</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>190</v>
@@ -6558,12 +6585,12 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="59"/>
+      <c r="A18" s="62"/>
       <c r="B18" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -6578,9 +6605,9 @@
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59"/>
+      <c r="A19" s="62"/>
       <c r="B19" s="15" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>158</v>
@@ -6598,7 +6625,7 @@
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="59"/>
+      <c r="A20" s="62"/>
       <c r="B20" s="15" t="s">
         <v>205</v>
       </c>
@@ -6618,14 +6645,14 @@
       <c r="N20" s="14"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="50" t="s">
+      <c r="A21" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="B21" s="51"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="52"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="54"/>
       <c r="G21" s="37"/>
       <c r="H21" s="37"/>
       <c r="I21" s="37"/>
@@ -6636,11 +6663,11 @@
       <c r="N21" s="14"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="60" t="s">
-        <v>435</v>
+      <c r="A22" s="63" t="s">
+        <v>433</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>154</v>
@@ -6658,9 +6685,9 @@
       <c r="N22" s="14"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="60"/>
+      <c r="A23" s="63"/>
       <c r="B23" s="15" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>120</v>
@@ -6678,9 +6705,9 @@
       <c r="N23" s="14"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="60"/>
+      <c r="A24" s="63"/>
       <c r="B24" s="15" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>123</v>
@@ -6698,9 +6725,9 @@
       <c r="N24" s="14"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="60"/>
+      <c r="A25" s="63"/>
       <c r="B25" s="15" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>126</v>
@@ -6718,9 +6745,9 @@
       <c r="N25" s="14"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="60"/>
+      <c r="A26" s="63"/>
       <c r="B26" s="15" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>129</v>
@@ -6738,9 +6765,9 @@
       <c r="N26" s="14"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="60"/>
+      <c r="A27" s="63"/>
       <c r="B27" s="15" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>149</v>
@@ -6758,9 +6785,9 @@
       <c r="N27" s="14"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="60"/>
+      <c r="A28" s="63"/>
       <c r="B28" s="15" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>124</v>
@@ -6778,9 +6805,9 @@
       <c r="N28" s="14"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="60"/>
+      <c r="A29" s="63"/>
       <c r="B29" s="15" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>165</v>
@@ -6798,9 +6825,9 @@
       <c r="N29" s="14"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="60"/>
+      <c r="A30" s="63"/>
       <c r="B30" s="15" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>128</v>
@@ -6818,9 +6845,9 @@
       <c r="N30" s="14"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="60"/>
+      <c r="A31" s="63"/>
       <c r="B31" s="15" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>161</v>
@@ -6838,9 +6865,9 @@
       <c r="N31" s="14"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="60"/>
+      <c r="A32" s="63"/>
       <c r="B32" s="15" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>90</v>
@@ -6858,9 +6885,9 @@
       <c r="N32" s="14"/>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="60"/>
+      <c r="A33" s="63"/>
       <c r="B33" s="15" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>89</v>
@@ -6878,9 +6905,9 @@
       <c r="N33" s="14"/>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="60"/>
+      <c r="A34" s="63"/>
       <c r="B34" s="15" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>155</v>
@@ -6898,9 +6925,9 @@
       <c r="N34" s="14"/>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="60"/>
+      <c r="A35" s="63"/>
       <c r="B35" s="15" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>122</v>
@@ -6918,9 +6945,9 @@
       <c r="N35" s="14"/>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="60"/>
+      <c r="A36" s="63"/>
       <c r="B36" s="15" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>162</v>
@@ -6938,9 +6965,9 @@
       <c r="N36" s="14"/>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="60"/>
+      <c r="A37" s="63"/>
       <c r="B37" s="15" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>125</v>
@@ -6958,9 +6985,9 @@
       <c r="N37" s="14"/>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="60"/>
+      <c r="A38" s="63"/>
       <c r="B38" s="15" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>131</v>
@@ -6978,9 +7005,9 @@
       <c r="N38" s="14"/>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="60"/>
+      <c r="A39" s="63"/>
       <c r="B39" s="15" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>153</v>
@@ -6998,9 +7025,9 @@
       <c r="N39" s="14"/>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="60"/>
+      <c r="A40" s="63"/>
       <c r="B40" s="15" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>160</v>
@@ -7018,9 +7045,9 @@
       <c r="N40" s="14"/>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="60"/>
+      <c r="A41" s="63"/>
       <c r="B41" s="15" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>133</v>
@@ -7038,9 +7065,9 @@
       <c r="N41" s="14"/>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="60"/>
+      <c r="A42" s="63"/>
       <c r="B42" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>121</v>
@@ -7058,9 +7085,9 @@
       <c r="N42" s="14"/>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="60"/>
+      <c r="A43" s="63"/>
       <c r="B43" s="15" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>130</v>
@@ -7078,9 +7105,9 @@
       <c r="N43" s="14"/>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="60"/>
+      <c r="A44" s="63"/>
       <c r="B44" s="15" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>127</v>
@@ -7098,9 +7125,9 @@
       <c r="N44" s="14"/>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="60"/>
+      <c r="A45" s="63"/>
       <c r="B45" s="15" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>91</v>
@@ -7118,14 +7145,14 @@
       <c r="N45" s="14"/>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="50" t="s">
+      <c r="A46" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="B46" s="51"/>
-      <c r="C46" s="51"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="52"/>
+      <c r="B46" s="53"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="54"/>
       <c r="G46" s="37"/>
       <c r="H46" s="37"/>
       <c r="I46" s="37"/>
@@ -7136,11 +7163,11 @@
       <c r="N46" s="14"/>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="59" t="s">
-        <v>463</v>
+      <c r="A47" s="62" t="s">
+        <v>461</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>51</v>
@@ -7158,9 +7185,9 @@
       <c r="N47" s="14"/>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="59"/>
+      <c r="A48" s="62"/>
       <c r="B48" s="15" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>48</v>
@@ -7178,9 +7205,9 @@
       <c r="N48" s="14"/>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="59"/>
+      <c r="A49" s="62"/>
       <c r="B49" s="15" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>45</v>
@@ -7198,9 +7225,9 @@
       <c r="N49" s="14"/>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="59"/>
+      <c r="A50" s="62"/>
       <c r="B50" s="15" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>34</v>
@@ -7218,9 +7245,9 @@
       <c r="N50" s="14"/>
     </row>
     <row r="51" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="59"/>
+      <c r="A51" s="62"/>
       <c r="B51" s="15" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>44</v>
@@ -7238,9 +7265,9 @@
       <c r="N51" s="14"/>
     </row>
     <row r="52" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="59"/>
+      <c r="A52" s="62"/>
       <c r="B52" s="15" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>53</v>
@@ -7258,11 +7285,11 @@
       <c r="N52" s="14"/>
     </row>
     <row r="53" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="59" t="s">
-        <v>459</v>
+      <c r="A53" s="62" t="s">
+        <v>457</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>54</v>
@@ -7280,9 +7307,9 @@
       <c r="N53" s="14"/>
     </row>
     <row r="54" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="59"/>
+      <c r="A54" s="62"/>
       <c r="B54" s="15" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>0</v>
@@ -7300,9 +7327,9 @@
       <c r="N54" s="14"/>
     </row>
     <row r="55" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="59"/>
+      <c r="A55" s="62"/>
       <c r="B55" s="15" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>39</v>
@@ -7320,9 +7347,9 @@
       <c r="N55" s="14"/>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="59"/>
+      <c r="A56" s="62"/>
       <c r="B56" s="15" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>23</v>
@@ -7340,9 +7367,9 @@
       <c r="N56" s="14"/>
     </row>
     <row r="57" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="59"/>
+      <c r="A57" s="62"/>
       <c r="B57" s="15" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>17</v>
@@ -7360,9 +7387,9 @@
       <c r="N57" s="14"/>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="59"/>
+      <c r="A58" s="62"/>
       <c r="B58" s="15" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>50</v>
@@ -7380,14 +7407,14 @@
       <c r="N58" s="14"/>
     </row>
     <row r="59" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="50" t="s">
+      <c r="A59" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="51"/>
-      <c r="C59" s="51"/>
-      <c r="D59" s="51"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="52"/>
+      <c r="B59" s="53"/>
+      <c r="C59" s="53"/>
+      <c r="D59" s="53"/>
+      <c r="E59" s="53"/>
+      <c r="F59" s="54"/>
       <c r="G59" s="37"/>
       <c r="H59" s="37"/>
       <c r="I59" s="37"/>
@@ -7398,11 +7425,11 @@
       <c r="N59" s="14"/>
     </row>
     <row r="60" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="59" t="s">
-        <v>515</v>
+      <c r="A60" s="62" t="s">
+        <v>513</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>7</v>
@@ -7420,9 +7447,9 @@
       <c r="N60" s="14"/>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="59"/>
+      <c r="A61" s="62"/>
       <c r="B61" s="15" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>136</v>
@@ -7440,9 +7467,9 @@
       <c r="N61" s="14"/>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="59"/>
+      <c r="A62" s="62"/>
       <c r="B62" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>137</v>
@@ -7460,9 +7487,9 @@
       <c r="N62" s="14"/>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="59"/>
+      <c r="A63" s="62"/>
       <c r="B63" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>22</v>
@@ -7480,14 +7507,14 @@
       <c r="N63" s="14"/>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="50" t="s">
+      <c r="A64" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="B64" s="51"/>
-      <c r="C64" s="51"/>
-      <c r="D64" s="51"/>
-      <c r="E64" s="51"/>
-      <c r="F64" s="52"/>
+      <c r="B64" s="53"/>
+      <c r="C64" s="53"/>
+      <c r="D64" s="53"/>
+      <c r="E64" s="53"/>
+      <c r="F64" s="54"/>
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
       <c r="I64" s="37"/>
@@ -7498,11 +7525,11 @@
       <c r="N64" s="14"/>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="59" t="s">
-        <v>448</v>
+      <c r="A65" s="62" t="s">
+        <v>446</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>156</v>
@@ -7520,9 +7547,9 @@
       <c r="N65" s="14"/>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="59"/>
+      <c r="A66" s="62"/>
       <c r="B66" s="15" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>143</v>
@@ -7540,9 +7567,9 @@
       <c r="N66" s="14"/>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="59"/>
+      <c r="A67" s="62"/>
       <c r="B67" s="15" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>88</v>
@@ -7560,9 +7587,9 @@
       <c r="N67" s="14"/>
     </row>
     <row r="68" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="59"/>
+      <c r="A68" s="62"/>
       <c r="B68" s="15" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>87</v>
@@ -7580,9 +7607,9 @@
       <c r="N68" s="14"/>
     </row>
     <row r="69" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="59"/>
+      <c r="A69" s="62"/>
       <c r="B69" s="15" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>104</v>
@@ -7600,9 +7627,9 @@
       <c r="N69" s="14"/>
     </row>
     <row r="70" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="59"/>
+      <c r="A70" s="62"/>
       <c r="B70" s="15" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>95</v>
@@ -7620,9 +7647,9 @@
       <c r="N70" s="14"/>
     </row>
     <row r="71" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="59"/>
+      <c r="A71" s="62"/>
       <c r="B71" s="15" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>107</v>
@@ -7640,9 +7667,9 @@
       <c r="N71" s="14"/>
     </row>
     <row r="72" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="59"/>
+      <c r="A72" s="62"/>
       <c r="B72" s="15" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>97</v>
@@ -7660,9 +7687,9 @@
       <c r="N72" s="14"/>
     </row>
     <row r="73" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="59"/>
+      <c r="A73" s="62"/>
       <c r="B73" s="15" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>106</v>
@@ -7680,9 +7707,9 @@
       <c r="N73" s="14"/>
     </row>
     <row r="74" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="59"/>
+      <c r="A74" s="62"/>
       <c r="B74" s="15" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>98</v>
@@ -7700,14 +7727,14 @@
       <c r="N74" s="14"/>
     </row>
     <row r="75" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="50" t="s">
+      <c r="A75" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="B75" s="51"/>
-      <c r="C75" s="51"/>
-      <c r="D75" s="51"/>
-      <c r="E75" s="51"/>
-      <c r="F75" s="52"/>
+      <c r="B75" s="53"/>
+      <c r="C75" s="53"/>
+      <c r="D75" s="53"/>
+      <c r="E75" s="53"/>
+      <c r="F75" s="54"/>
       <c r="G75" s="37"/>
       <c r="H75" s="37"/>
       <c r="I75" s="37"/>
@@ -7718,11 +7745,11 @@
       <c r="N75" s="14"/>
     </row>
     <row r="76" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="59" t="s">
-        <v>219</v>
+      <c r="A76" s="62" t="s">
+        <v>218</v>
       </c>
       <c r="B76" s="28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>13</v>
@@ -7740,9 +7767,9 @@
       <c r="N76" s="14"/>
     </row>
     <row r="77" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="59"/>
+      <c r="A77" s="62"/>
       <c r="B77" s="28" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>52</v>
@@ -7760,14 +7787,14 @@
       <c r="N77" s="14"/>
     </row>
     <row r="78" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="50" t="s">
+      <c r="A78" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="B78" s="51"/>
-      <c r="C78" s="51"/>
-      <c r="D78" s="51"/>
-      <c r="E78" s="51"/>
-      <c r="F78" s="52"/>
+      <c r="B78" s="53"/>
+      <c r="C78" s="53"/>
+      <c r="D78" s="53"/>
+      <c r="E78" s="53"/>
+      <c r="F78" s="54"/>
       <c r="G78" s="37"/>
       <c r="H78" s="37"/>
       <c r="I78" s="37"/>
@@ -7778,9 +7805,9 @@
       <c r="N78" s="14"/>
     </row>
     <row r="79" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="59"/>
+      <c r="A79" s="62"/>
       <c r="B79" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>185</v>
@@ -7798,7 +7825,7 @@
       <c r="N79" s="14"/>
     </row>
     <row r="80" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="59"/>
+      <c r="A80" s="62"/>
       <c r="B80" s="15" t="s">
         <v>178</v>
       </c>
@@ -7818,12 +7845,12 @@
       <c r="N80" s="14"/>
     </row>
     <row r="81" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="59"/>
+      <c r="A81" s="62"/>
       <c r="B81" s="15" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
@@ -7838,7 +7865,7 @@
       <c r="N81" s="14"/>
     </row>
     <row r="82" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="59"/>
+      <c r="A82" s="62"/>
       <c r="B82" s="15" t="s">
         <v>198</v>
       </c>
@@ -7858,9 +7885,9 @@
       <c r="N82" s="14"/>
     </row>
     <row r="83" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="59"/>
+      <c r="A83" s="62"/>
       <c r="B83" s="15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>171</v>
@@ -7878,12 +7905,12 @@
       <c r="N83" s="14"/>
     </row>
     <row r="84" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="59"/>
+      <c r="A84" s="62"/>
       <c r="B84" s="29" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -7898,12 +7925,12 @@
       <c r="N84" s="14"/>
     </row>
     <row r="85" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="59"/>
+      <c r="A85" s="62"/>
       <c r="B85" s="29" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
@@ -7918,12 +7945,12 @@
       <c r="N85" s="14"/>
     </row>
     <row r="86" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="59"/>
+      <c r="A86" s="62"/>
       <c r="B86" s="29" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -7938,14 +7965,14 @@
       <c r="N86" s="14"/>
     </row>
     <row r="87" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="50" t="s">
+      <c r="A87" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="B87" s="51"/>
-      <c r="C87" s="51"/>
-      <c r="D87" s="51"/>
-      <c r="E87" s="51"/>
-      <c r="F87" s="52"/>
+      <c r="B87" s="53"/>
+      <c r="C87" s="53"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="54"/>
       <c r="G87" s="37"/>
       <c r="H87" s="37"/>
       <c r="I87" s="37"/>
@@ -7956,14 +7983,14 @@
       <c r="N87" s="14"/>
     </row>
     <row r="88" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="59" t="s">
-        <v>513</v>
+      <c r="A88" s="62" t="s">
+        <v>511</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
@@ -7978,12 +8005,12 @@
       <c r="N88" s="14"/>
     </row>
     <row r="89" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="59"/>
+      <c r="A89" s="62"/>
       <c r="B89" s="15" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
@@ -7998,12 +8025,12 @@
       <c r="N89" s="14"/>
     </row>
     <row r="90" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="59"/>
+      <c r="A90" s="62"/>
       <c r="B90" s="15" t="s">
         <v>199</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -8018,12 +8045,12 @@
       <c r="N90" s="14"/>
     </row>
     <row r="91" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="59"/>
+      <c r="A91" s="62"/>
       <c r="B91" s="28" t="s">
         <v>189</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
@@ -8038,12 +8065,12 @@
       <c r="N91" s="14"/>
     </row>
     <row r="92" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="59"/>
+      <c r="A92" s="62"/>
       <c r="B92" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -8058,12 +8085,12 @@
       <c r="N92" s="14"/>
     </row>
     <row r="93" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="59"/>
+      <c r="A93" s="62"/>
       <c r="B93" s="15" t="s">
         <v>200</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
@@ -8078,12 +8105,12 @@
       <c r="N93" s="14"/>
     </row>
     <row r="94" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="59"/>
+      <c r="A94" s="62"/>
       <c r="B94" s="28" t="s">
         <v>213</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
@@ -8098,14 +8125,14 @@
       <c r="N94" s="14"/>
     </row>
     <row r="95" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="59" t="s">
-        <v>513</v>
+      <c r="A95" s="62" t="s">
+        <v>511</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
@@ -8120,12 +8147,12 @@
       <c r="N95" s="14"/>
     </row>
     <row r="96" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="59"/>
+      <c r="A96" s="62"/>
       <c r="B96" s="15" t="s">
         <v>172</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
@@ -8140,12 +8167,12 @@
       <c r="N96" s="14"/>
     </row>
     <row r="97" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="59"/>
+      <c r="A97" s="62"/>
       <c r="B97" s="15" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -8160,12 +8187,12 @@
       <c r="N97" s="14"/>
     </row>
     <row r="98" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="59"/>
+      <c r="A98" s="62"/>
       <c r="B98" s="15" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
@@ -8180,12 +8207,12 @@
       <c r="N98" s="14"/>
     </row>
     <row r="99" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="59"/>
+      <c r="A99" s="62"/>
       <c r="B99" s="15" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
@@ -8200,12 +8227,12 @@
       <c r="N99" s="14"/>
     </row>
     <row r="100" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="59"/>
+      <c r="A100" s="62"/>
       <c r="B100" s="15" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
@@ -8220,12 +8247,12 @@
       <c r="N100" s="14"/>
     </row>
     <row r="101" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="59"/>
+      <c r="A101" s="62"/>
       <c r="B101" s="15" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -8240,7 +8267,7 @@
       <c r="N101" s="14"/>
     </row>
     <row r="102" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="59"/>
+      <c r="A102" s="62"/>
       <c r="B102" s="15" t="s">
         <v>170</v>
       </c>
@@ -8260,9 +8287,9 @@
       <c r="N102" s="14"/>
     </row>
     <row r="103" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="59"/>
+      <c r="A103" s="62"/>
       <c r="B103" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>109</v>
@@ -8280,14 +8307,14 @@
       <c r="N103" s="14"/>
     </row>
     <row r="104" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="50" t="s">
+      <c r="A104" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="B104" s="51"/>
-      <c r="C104" s="51"/>
-      <c r="D104" s="51"/>
-      <c r="E104" s="51"/>
-      <c r="F104" s="52"/>
+      <c r="B104" s="53"/>
+      <c r="C104" s="53"/>
+      <c r="D104" s="53"/>
+      <c r="E104" s="53"/>
+      <c r="F104" s="54"/>
       <c r="G104" s="37"/>
       <c r="H104" s="37"/>
       <c r="I104" s="37"/>
@@ -8299,10 +8326,10 @@
     </row>
     <row r="105" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="14" t="s">
-        <v>726</v>
+        <v>711</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>159</v>
@@ -8321,13 +8348,13 @@
     </row>
     <row r="106" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B106" s="15" t="s">
         <v>203</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
@@ -8342,8 +8369,8 @@
       <c r="N106" s="14"/>
     </row>
     <row r="107" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="59" t="s">
-        <v>259</v>
+      <c r="A107" s="62" t="s">
+        <v>258</v>
       </c>
       <c r="B107" s="15" t="s">
         <v>208</v>
@@ -8364,9 +8391,9 @@
       <c r="N107" s="14"/>
     </row>
     <row r="108" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="59"/>
+      <c r="A108" s="62"/>
       <c r="B108" s="28" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>67</v>
@@ -8384,9 +8411,9 @@
       <c r="N108" s="14"/>
     </row>
     <row r="109" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="59"/>
+      <c r="A109" s="62"/>
       <c r="B109" s="28" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>85</v>
@@ -8408,7 +8435,7 @@
         <v>207</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>2</v>
@@ -8426,14 +8453,14 @@
       <c r="N110" s="14"/>
     </row>
     <row r="111" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="50" t="s">
+      <c r="A111" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="B111" s="51"/>
-      <c r="C111" s="51"/>
-      <c r="D111" s="51"/>
-      <c r="E111" s="51"/>
-      <c r="F111" s="52"/>
+      <c r="B111" s="53"/>
+      <c r="C111" s="53"/>
+      <c r="D111" s="53"/>
+      <c r="E111" s="53"/>
+      <c r="F111" s="54"/>
       <c r="G111" s="37"/>
       <c r="H111" s="37"/>
       <c r="I111" s="37"/>
@@ -8444,14 +8471,14 @@
       <c r="N111" s="14"/>
     </row>
     <row r="112" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="60" t="s">
+      <c r="A112" s="63" t="s">
         <v>49</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
@@ -8466,12 +8493,12 @@
       <c r="N112" s="14"/>
     </row>
     <row r="113" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="60"/>
+      <c r="A113" s="63"/>
       <c r="B113" s="15" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
@@ -8486,12 +8513,12 @@
       <c r="N113" s="14"/>
     </row>
     <row r="114" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="60"/>
+      <c r="A114" s="63"/>
       <c r="B114" s="15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
@@ -8506,12 +8533,12 @@
       <c r="N114" s="14"/>
     </row>
     <row r="115" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="60"/>
+      <c r="A115" s="63"/>
       <c r="B115" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
@@ -8526,12 +8553,12 @@
       <c r="N115" s="14"/>
     </row>
     <row r="116" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="60"/>
+      <c r="A116" s="63"/>
       <c r="B116" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
@@ -8546,12 +8573,12 @@
       <c r="N116" s="14"/>
     </row>
     <row r="117" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="60"/>
+      <c r="A117" s="63"/>
       <c r="B117" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
@@ -8566,12 +8593,12 @@
       <c r="N117" s="14"/>
     </row>
     <row r="118" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="60"/>
+      <c r="A118" s="63"/>
       <c r="B118" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
@@ -8586,12 +8613,12 @@
       <c r="N118" s="14"/>
     </row>
     <row r="119" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="60"/>
+      <c r="A119" s="63"/>
       <c r="B119" s="15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
@@ -8606,14 +8633,14 @@
       <c r="N119" s="14"/>
     </row>
     <row r="120" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="50" t="s">
+      <c r="A120" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="B120" s="51"/>
-      <c r="C120" s="51"/>
-      <c r="D120" s="51"/>
-      <c r="E120" s="51"/>
-      <c r="F120" s="52"/>
+      <c r="B120" s="53"/>
+      <c r="C120" s="53"/>
+      <c r="D120" s="53"/>
+      <c r="E120" s="53"/>
+      <c r="F120" s="54"/>
       <c r="G120" s="37"/>
       <c r="H120" s="37"/>
       <c r="I120" s="37"/>
@@ -8624,11 +8651,11 @@
       <c r="N120" s="14"/>
     </row>
     <row r="121" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="59" t="s">
-        <v>514</v>
+      <c r="A121" s="62" t="s">
+        <v>512</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>111</v>
@@ -8646,9 +8673,9 @@
       <c r="N121" s="14"/>
     </row>
     <row r="122" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="59"/>
+      <c r="A122" s="62"/>
       <c r="B122" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>100</v>
@@ -8666,9 +8693,9 @@
       <c r="N122" s="14"/>
     </row>
     <row r="123" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="59"/>
+      <c r="A123" s="62"/>
       <c r="B123" s="15" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>112</v>
@@ -8686,9 +8713,9 @@
       <c r="N123" s="14"/>
     </row>
     <row r="124" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="59"/>
+      <c r="A124" s="62"/>
       <c r="B124" s="15" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>113</v>
@@ -8706,14 +8733,14 @@
       <c r="N124" s="14"/>
     </row>
     <row r="125" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="50" t="s">
+      <c r="A125" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="B125" s="51"/>
-      <c r="C125" s="51"/>
-      <c r="D125" s="51"/>
-      <c r="E125" s="51"/>
-      <c r="F125" s="52"/>
+      <c r="B125" s="53"/>
+      <c r="C125" s="53"/>
+      <c r="D125" s="53"/>
+      <c r="E125" s="53"/>
+      <c r="F125" s="54"/>
       <c r="G125" s="37"/>
       <c r="H125" s="37"/>
       <c r="I125" s="37"/>
@@ -8724,11 +8751,11 @@
       <c r="N125" s="14"/>
     </row>
     <row r="126" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="59" t="s">
-        <v>281</v>
+      <c r="A126" s="62" t="s">
+        <v>280</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>18</v>
@@ -8746,9 +8773,9 @@
       <c r="N126" s="14"/>
     </row>
     <row r="127" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="59"/>
+      <c r="A127" s="62"/>
       <c r="B127" s="15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>142</v>
@@ -8766,14 +8793,14 @@
       <c r="N127" s="14"/>
     </row>
     <row r="128" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="53" t="s">
+      <c r="A128" s="86" t="s">
         <v>114</v>
       </c>
-      <c r="B128" s="54"/>
-      <c r="C128" s="54"/>
-      <c r="D128" s="54"/>
-      <c r="E128" s="54"/>
-      <c r="F128" s="55"/>
+      <c r="B128" s="87"/>
+      <c r="C128" s="87"/>
+      <c r="D128" s="87"/>
+      <c r="E128" s="87"/>
+      <c r="F128" s="88"/>
       <c r="G128" s="46"/>
       <c r="H128" s="46"/>
       <c r="I128" s="46"/>
@@ -8784,14 +8811,14 @@
       <c r="N128" s="21"/>
     </row>
     <row r="129" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="56" t="s">
+      <c r="A129" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="B129" s="57"/>
-      <c r="C129" s="57"/>
-      <c r="D129" s="57"/>
-      <c r="E129" s="57"/>
-      <c r="F129" s="58"/>
+      <c r="B129" s="90"/>
+      <c r="C129" s="90"/>
+      <c r="D129" s="90"/>
+      <c r="E129" s="90"/>
+      <c r="F129" s="91"/>
       <c r="G129" s="47"/>
       <c r="H129" s="47"/>
       <c r="I129" s="47"/>
@@ -8821,90 +8848,106 @@
       <c r="A131" s="3"/>
       <c r="B131" s="1"/>
       <c r="C131" s="5"/>
-      <c r="D131" s="70"/>
-      <c r="E131" s="71"/>
-      <c r="F131" s="71"/>
-      <c r="G131" s="63"/>
-      <c r="H131" s="63"/>
-      <c r="I131" s="63"/>
-      <c r="J131" s="64"/>
+      <c r="D131" s="82"/>
+      <c r="E131" s="83"/>
+      <c r="F131" s="83"/>
+      <c r="G131" s="75"/>
+      <c r="H131" s="75"/>
+      <c r="I131" s="75"/>
+      <c r="J131" s="76"/>
       <c r="K131" s="8"/>
       <c r="L131" s="8"/>
       <c r="M131" s="8"/>
       <c r="N131" s="8"/>
     </row>
     <row r="132" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D132" s="72" t="s">
-        <v>682</v>
-      </c>
-      <c r="E132" s="73"/>
-      <c r="F132" s="73"/>
-      <c r="G132" s="65"/>
-      <c r="H132" s="65"/>
-      <c r="I132" s="65"/>
-      <c r="J132" s="66"/>
+      <c r="D132" s="84" t="s">
+        <v>667</v>
+      </c>
+      <c r="E132" s="85"/>
+      <c r="F132" s="85"/>
+      <c r="G132" s="77"/>
+      <c r="H132" s="77"/>
+      <c r="I132" s="77"/>
+      <c r="J132" s="78"/>
     </row>
     <row r="133" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D133" s="74" t="s">
-        <v>683</v>
-      </c>
-      <c r="E133" s="75"/>
-      <c r="F133" s="75"/>
-      <c r="G133" s="59"/>
-      <c r="H133" s="59"/>
-      <c r="I133" s="59"/>
-      <c r="J133" s="68"/>
+      <c r="D133" s="66" t="s">
+        <v>668</v>
+      </c>
+      <c r="E133" s="67"/>
+      <c r="F133" s="67"/>
+      <c r="G133" s="62"/>
+      <c r="H133" s="62"/>
+      <c r="I133" s="62"/>
+      <c r="J133" s="80"/>
     </row>
     <row r="134" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D134" s="74" t="s">
-        <v>684</v>
-      </c>
-      <c r="E134" s="75"/>
-      <c r="F134" s="75"/>
-      <c r="G134" s="59"/>
-      <c r="H134" s="59"/>
-      <c r="I134" s="59"/>
-      <c r="J134" s="68"/>
+      <c r="D134" s="66" t="s">
+        <v>669</v>
+      </c>
+      <c r="E134" s="67"/>
+      <c r="F134" s="67"/>
+      <c r="G134" s="62"/>
+      <c r="H134" s="62"/>
+      <c r="I134" s="62"/>
+      <c r="J134" s="80"/>
     </row>
     <row r="135" spans="1:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D135" s="76" t="s">
-        <v>685</v>
-      </c>
-      <c r="E135" s="77"/>
-      <c r="F135" s="77"/>
-      <c r="G135" s="67"/>
-      <c r="H135" s="67"/>
-      <c r="I135" s="67"/>
-      <c r="J135" s="69"/>
+      <c r="D135" s="68" t="s">
+        <v>670</v>
+      </c>
+      <c r="E135" s="69"/>
+      <c r="F135" s="69"/>
+      <c r="G135" s="79"/>
+      <c r="H135" s="79"/>
+      <c r="I135" s="79"/>
+      <c r="J135" s="81"/>
     </row>
     <row r="136" spans="1:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D136" s="61" t="s">
-        <v>686</v>
-      </c>
-      <c r="E136" s="62"/>
-      <c r="F136" s="62"/>
-      <c r="G136" s="63"/>
-      <c r="H136" s="63"/>
-      <c r="I136" s="63"/>
-      <c r="J136" s="63"/>
+      <c r="D136" s="73" t="s">
+        <v>671</v>
+      </c>
+      <c r="E136" s="74"/>
+      <c r="F136" s="74"/>
+      <c r="G136" s="75"/>
+      <c r="H136" s="75"/>
+      <c r="I136" s="75"/>
+      <c r="J136" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="A8:A15"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A22:A45"/>
-    <mergeCell ref="A53:A58"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="A65:A74"/>
-    <mergeCell ref="A47:A52"/>
-    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A120:F120"/>
+    <mergeCell ref="A125:F125"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A129:F129"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A103"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A112:A119"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A104:F104"/>
+    <mergeCell ref="A111:F111"/>
+    <mergeCell ref="D136:F136"/>
+    <mergeCell ref="G131:H131"/>
+    <mergeCell ref="I131:J131"/>
+    <mergeCell ref="G132:H132"/>
+    <mergeCell ref="I132:J132"/>
+    <mergeCell ref="G133:H133"/>
+    <mergeCell ref="G134:H134"/>
+    <mergeCell ref="G135:H135"/>
+    <mergeCell ref="G136:H136"/>
+    <mergeCell ref="I133:J133"/>
+    <mergeCell ref="I134:J134"/>
+    <mergeCell ref="I135:J135"/>
+    <mergeCell ref="I136:J136"/>
+    <mergeCell ref="D131:F131"/>
+    <mergeCell ref="D132:F132"/>
+    <mergeCell ref="D133:F133"/>
     <mergeCell ref="D134:F134"/>
     <mergeCell ref="D135:F135"/>
     <mergeCell ref="L6:L7"/>
@@ -8921,37 +8964,21 @@
     <mergeCell ref="A126:A127"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="A79:A86"/>
-    <mergeCell ref="D136:F136"/>
-    <mergeCell ref="G131:H131"/>
-    <mergeCell ref="I131:J131"/>
-    <mergeCell ref="G132:H132"/>
-    <mergeCell ref="I132:J132"/>
-    <mergeCell ref="G133:H133"/>
-    <mergeCell ref="G134:H134"/>
-    <mergeCell ref="G135:H135"/>
-    <mergeCell ref="G136:H136"/>
-    <mergeCell ref="I133:J133"/>
-    <mergeCell ref="I134:J134"/>
-    <mergeCell ref="I135:J135"/>
-    <mergeCell ref="I136:J136"/>
-    <mergeCell ref="D131:F131"/>
-    <mergeCell ref="D132:F132"/>
-    <mergeCell ref="D133:F133"/>
-    <mergeCell ref="A120:F120"/>
-    <mergeCell ref="A125:F125"/>
-    <mergeCell ref="A128:F128"/>
-    <mergeCell ref="A129:F129"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A75:F75"/>
-    <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A103"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A112:A119"/>
-    <mergeCell ref="A87:F87"/>
-    <mergeCell ref="A104:F104"/>
-    <mergeCell ref="A111:F111"/>
+    <mergeCell ref="A22:A45"/>
+    <mergeCell ref="A53:A58"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="A65:A74"/>
+    <mergeCell ref="A47:A52"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="A8:A15"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A16:F16"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11436,20 +11463,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="80"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30"/>
@@ -11465,13 +11492,13 @@
       <c r="K3" s="30"/>
       <c r="L3" s="30"/>
       <c r="M3" s="31" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="N3" s="49"/>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M4" s="36" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="N4" s="49"/>
     </row>
@@ -11480,71 +11507,71 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88" t="s">
-        <v>414</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>624</v>
-      </c>
-      <c r="C6" s="83" t="s">
+      <c r="A6" s="64" t="s">
+        <v>412</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>616</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>617</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>618</v>
+      </c>
+      <c r="E6" s="59" t="s">
+        <v>619</v>
+      </c>
+      <c r="F6" s="55" t="s">
+        <v>620</v>
+      </c>
+      <c r="G6" s="55" t="s">
+        <v>575</v>
+      </c>
+      <c r="H6" s="55" t="s">
+        <v>579</v>
+      </c>
+      <c r="I6" s="55" t="s">
+        <v>585</v>
+      </c>
+      <c r="J6" s="55" t="s">
+        <v>586</v>
+      </c>
+      <c r="K6" s="55" t="s">
+        <v>587</v>
+      </c>
+      <c r="L6" s="55" t="s">
+        <v>600</v>
+      </c>
+      <c r="M6" s="55" t="s">
+        <v>621</v>
+      </c>
+      <c r="N6" s="71" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="65"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="72"/>
+    </row>
+    <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="95" t="s">
         <v>625</v>
       </c>
-      <c r="D6" s="83" t="s">
-        <v>626</v>
-      </c>
-      <c r="E6" s="83" t="s">
-        <v>627</v>
-      </c>
-      <c r="F6" s="78" t="s">
-        <v>628</v>
-      </c>
-      <c r="G6" s="78" t="s">
-        <v>578</v>
-      </c>
-      <c r="H6" s="78" t="s">
-        <v>582</v>
-      </c>
-      <c r="I6" s="78" t="s">
-        <v>588</v>
-      </c>
-      <c r="J6" s="78" t="s">
-        <v>589</v>
-      </c>
-      <c r="K6" s="78" t="s">
-        <v>590</v>
-      </c>
-      <c r="L6" s="78" t="s">
-        <v>608</v>
-      </c>
-      <c r="M6" s="78" t="s">
-        <v>629</v>
-      </c>
-      <c r="N6" s="81" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="89"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="84"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="79"/>
-      <c r="K7" s="79"/>
-      <c r="L7" s="79"/>
-      <c r="M7" s="79"/>
-      <c r="N7" s="82"/>
-    </row>
-    <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="94" t="s">
-        <v>633</v>
-      </c>
       <c r="B8" s="12" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>68</v>
@@ -11562,12 +11589,12 @@
       <c r="N8" s="26"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="91"/>
+      <c r="A9" s="92"/>
       <c r="B9" s="13" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -11582,12 +11609,12 @@
       <c r="N9" s="25"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="91"/>
+      <c r="A10" s="92"/>
       <c r="B10" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="18"/>
@@ -11602,12 +11629,12 @@
       <c r="N10" s="25"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="91"/>
+      <c r="A11" s="92"/>
       <c r="B11" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
@@ -11622,12 +11649,12 @@
       <c r="N11" s="25"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="91"/>
+      <c r="A12" s="92"/>
       <c r="B12" s="11" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
@@ -11642,9 +11669,9 @@
       <c r="N12" s="25"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="91"/>
+      <c r="A13" s="92"/>
       <c r="B13" s="11" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>38</v>
@@ -11662,9 +11689,9 @@
       <c r="N13" s="25"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="91"/>
+      <c r="A14" s="92"/>
       <c r="B14" s="11" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>167</v>
@@ -11682,12 +11709,12 @@
       <c r="N14" s="25"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="91"/>
+      <c r="A15" s="92"/>
       <c r="B15" s="11" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -11702,12 +11729,12 @@
       <c r="N15" s="25"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="91"/>
+      <c r="A16" s="92"/>
       <c r="B16" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -11722,12 +11749,12 @@
       <c r="N16" s="25"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="91"/>
+      <c r="A17" s="92"/>
       <c r="B17" s="11" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -11742,9 +11769,9 @@
       <c r="N17" s="25"/>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="91"/>
+      <c r="A18" s="92"/>
       <c r="B18" s="11" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>47</v>
@@ -11762,12 +11789,12 @@
       <c r="N18" s="25"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="91"/>
+      <c r="A19" s="92"/>
       <c r="B19" s="11" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -11782,14 +11809,14 @@
       <c r="N19" s="25"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="92" t="s">
+      <c r="A20" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="52"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="54"/>
       <c r="G20" s="37"/>
       <c r="H20" s="37"/>
       <c r="I20" s="37"/>
@@ -11800,11 +11827,11 @@
       <c r="N20" s="25"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="91" t="s">
-        <v>635</v>
+      <c r="A21" s="92" t="s">
+        <v>627</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>141</v>
@@ -11822,9 +11849,9 @@
       <c r="N21" s="25"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="91"/>
+      <c r="A22" s="92"/>
       <c r="B22" s="39" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>35</v>
@@ -11842,12 +11869,12 @@
       <c r="N22" s="25"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="91"/>
+      <c r="A23" s="92"/>
       <c r="B23" s="38" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -11862,12 +11889,12 @@
       <c r="N23" s="25"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="91"/>
+      <c r="A24" s="92"/>
       <c r="B24" s="38" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -11882,9 +11909,9 @@
       <c r="N24" s="25"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="91"/>
+      <c r="A25" s="92"/>
       <c r="B25" s="38" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>102</v>
@@ -11902,9 +11929,9 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="91"/>
+      <c r="A26" s="92"/>
       <c r="B26" s="38" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>31</v>
@@ -11922,9 +11949,9 @@
       <c r="N26" s="25"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="91"/>
+      <c r="A27" s="92"/>
       <c r="B27" s="38" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>29</v>
@@ -11942,9 +11969,9 @@
       <c r="N27" s="25"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="91"/>
+      <c r="A28" s="92"/>
       <c r="B28" s="38" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>26</v>
@@ -11962,14 +11989,14 @@
       <c r="N28" s="25"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="92" t="s">
+      <c r="A29" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="52"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54"/>
       <c r="G29" s="37"/>
       <c r="H29" s="37"/>
       <c r="I29" s="37"/>
@@ -11980,14 +12007,14 @@
       <c r="N29" s="25"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="91" t="s">
-        <v>637</v>
+      <c r="A30" s="92" t="s">
+        <v>629</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
@@ -12002,12 +12029,12 @@
       <c r="N30" s="25"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="91"/>
+      <c r="A31" s="92"/>
       <c r="B31" s="40" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
@@ -12022,12 +12049,12 @@
       <c r="N31" s="25"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="91"/>
+      <c r="A32" s="92"/>
       <c r="B32" s="42" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
@@ -12042,12 +12069,12 @@
       <c r="N32" s="25"/>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="91"/>
+      <c r="A33" s="92"/>
       <c r="B33" s="40" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
@@ -12062,14 +12089,14 @@
       <c r="N33" s="25"/>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="92" t="s">
+      <c r="A34" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="51"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="52"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="54"/>
       <c r="G34" s="37"/>
       <c r="H34" s="37"/>
       <c r="I34" s="37"/>
@@ -12080,11 +12107,11 @@
       <c r="N34" s="25"/>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="90" t="s">
-        <v>638</v>
+      <c r="A35" s="93" t="s">
+        <v>630</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>65</v>
@@ -12102,9 +12129,9 @@
       <c r="N35" s="25"/>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="90"/>
+      <c r="A36" s="93"/>
       <c r="B36" s="39" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>103</v>
@@ -12122,9 +12149,9 @@
       <c r="N36" s="25"/>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="90"/>
+      <c r="A37" s="93"/>
       <c r="B37" s="38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>60</v>
@@ -12142,7 +12169,7 @@
       <c r="N37" s="25"/>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="90"/>
+      <c r="A38" s="93"/>
       <c r="B38" s="38" t="s">
         <v>211</v>
       </c>
@@ -12162,9 +12189,9 @@
       <c r="N38" s="25"/>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="90"/>
+      <c r="A39" s="93"/>
       <c r="B39" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>62</v>
@@ -12182,7 +12209,7 @@
       <c r="N39" s="25"/>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="90"/>
+      <c r="A40" s="93"/>
       <c r="B40" s="38" t="s">
         <v>204</v>
       </c>
@@ -12202,9 +12229,9 @@
       <c r="N40" s="25"/>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="90"/>
+      <c r="A41" s="93"/>
       <c r="B41" s="38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>92</v>
@@ -12222,9 +12249,9 @@
       <c r="N41" s="25"/>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="90"/>
+      <c r="A42" s="93"/>
       <c r="B42" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C42" s="10" t="s">
         <v>101</v>
@@ -12242,9 +12269,9 @@
       <c r="N42" s="25"/>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="90"/>
+      <c r="A43" s="93"/>
       <c r="B43" s="38" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>37</v>
@@ -12262,9 +12289,9 @@
       <c r="N43" s="25"/>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="90"/>
+      <c r="A44" s="93"/>
       <c r="B44" s="38" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>12</v>
@@ -12282,7 +12309,7 @@
       <c r="N44" s="25"/>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="90"/>
+      <c r="A45" s="93"/>
       <c r="B45" s="38" t="s">
         <v>212</v>
       </c>
@@ -12302,9 +12329,9 @@
       <c r="N45" s="25"/>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="90"/>
+      <c r="A46" s="93"/>
       <c r="B46" s="38" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>64</v>
@@ -12322,14 +12349,14 @@
       <c r="N46" s="25"/>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="92" t="s">
+      <c r="A47" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B47" s="51"/>
-      <c r="C47" s="51"/>
-      <c r="D47" s="51"/>
-      <c r="E47" s="51"/>
-      <c r="F47" s="52"/>
+      <c r="B47" s="53"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="53"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="54"/>
       <c r="G47" s="37"/>
       <c r="H47" s="37"/>
       <c r="I47" s="37"/>
@@ -12340,14 +12367,14 @@
       <c r="N47" s="25"/>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="90" t="s">
-        <v>639</v>
+      <c r="A48" s="93" t="s">
+        <v>631</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -12362,12 +12389,12 @@
       <c r="N48" s="25"/>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="90"/>
+      <c r="A49" s="93"/>
       <c r="B49" s="15" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -12382,12 +12409,12 @@
       <c r="N49" s="25"/>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="90"/>
+      <c r="A50" s="93"/>
       <c r="B50" s="15" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -12402,9 +12429,9 @@
       <c r="N50" s="25"/>
     </row>
     <row r="51" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="90"/>
+      <c r="A51" s="93"/>
       <c r="B51" s="15" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>86</v>
@@ -12422,12 +12449,12 @@
       <c r="N51" s="25"/>
     </row>
     <row r="52" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="90"/>
+      <c r="A52" s="93"/>
       <c r="B52" s="15" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -12442,12 +12469,12 @@
       <c r="N52" s="25"/>
     </row>
     <row r="53" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="90"/>
+      <c r="A53" s="93"/>
       <c r="B53" s="15" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -12462,12 +12489,12 @@
       <c r="N53" s="25"/>
     </row>
     <row r="54" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="90"/>
+      <c r="A54" s="93"/>
       <c r="B54" s="15" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -12482,12 +12509,12 @@
       <c r="N54" s="25"/>
     </row>
     <row r="55" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="90"/>
+      <c r="A55" s="93"/>
       <c r="B55" s="15" t="s">
         <v>182</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -12502,12 +12529,12 @@
       <c r="N55" s="25"/>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="90"/>
+      <c r="A56" s="93"/>
       <c r="B56" s="15" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -12522,12 +12549,12 @@
       <c r="N56" s="25"/>
     </row>
     <row r="57" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="91"/>
+      <c r="A57" s="92"/>
       <c r="B57" s="15" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -12542,9 +12569,9 @@
       <c r="N57" s="25"/>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="91"/>
+      <c r="A58" s="92"/>
       <c r="B58" s="15" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>66</v>
@@ -12562,14 +12589,14 @@
       <c r="N58" s="25"/>
     </row>
     <row r="59" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="92" t="s">
+      <c r="A59" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="51"/>
-      <c r="C59" s="51"/>
-      <c r="D59" s="51"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="52"/>
+      <c r="B59" s="53"/>
+      <c r="C59" s="53"/>
+      <c r="D59" s="53"/>
+      <c r="E59" s="53"/>
+      <c r="F59" s="54"/>
       <c r="G59" s="37"/>
       <c r="H59" s="37"/>
       <c r="I59" s="37"/>
@@ -12580,11 +12607,11 @@
       <c r="N59" s="25"/>
     </row>
     <row r="60" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="90" t="s">
-        <v>641</v>
+      <c r="A60" s="93" t="s">
+        <v>633</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>73</v>
@@ -12602,12 +12629,12 @@
       <c r="N60" s="25"/>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="91"/>
+      <c r="A61" s="92"/>
       <c r="B61" s="15" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -12622,12 +12649,12 @@
       <c r="N61" s="25"/>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="91"/>
+      <c r="A62" s="92"/>
       <c r="B62" s="15" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -12642,12 +12669,12 @@
       <c r="N62" s="25"/>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="91"/>
+      <c r="A63" s="92"/>
       <c r="B63" s="15" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -12662,12 +12689,12 @@
       <c r="N63" s="25"/>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="91"/>
+      <c r="A64" s="92"/>
       <c r="B64" s="15" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -12682,12 +12709,12 @@
       <c r="N64" s="25"/>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="91"/>
+      <c r="A65" s="92"/>
       <c r="B65" s="15" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -12702,12 +12729,12 @@
       <c r="N65" s="25"/>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="91"/>
+      <c r="A66" s="92"/>
       <c r="B66" s="15" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -12722,12 +12749,12 @@
       <c r="N66" s="25"/>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="91"/>
+      <c r="A67" s="92"/>
       <c r="B67" s="15" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
@@ -12742,9 +12769,9 @@
       <c r="N67" s="25"/>
     </row>
     <row r="68" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="91"/>
+      <c r="A68" s="92"/>
       <c r="B68" s="15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>74</v>
@@ -12762,12 +12789,12 @@
       <c r="N68" s="25"/>
     </row>
     <row r="69" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="91"/>
+      <c r="A69" s="92"/>
       <c r="B69" s="15" t="s">
         <v>177</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -12782,12 +12809,12 @@
       <c r="N69" s="25"/>
     </row>
     <row r="70" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="91"/>
+      <c r="A70" s="92"/>
       <c r="B70" s="15" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -12802,12 +12829,12 @@
       <c r="N70" s="25"/>
     </row>
     <row r="71" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="91"/>
+      <c r="A71" s="92"/>
       <c r="B71" s="15" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -12822,12 +12849,12 @@
       <c r="N71" s="25"/>
     </row>
     <row r="72" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="91"/>
+      <c r="A72" s="92"/>
       <c r="B72" s="15" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -12842,12 +12869,12 @@
       <c r="N72" s="25"/>
     </row>
     <row r="73" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="91"/>
+      <c r="A73" s="92"/>
       <c r="B73" s="15" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
@@ -12862,12 +12889,12 @@
       <c r="N73" s="25"/>
     </row>
     <row r="74" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="91"/>
+      <c r="A74" s="92"/>
       <c r="B74" s="15" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -12882,14 +12909,14 @@
       <c r="N74" s="25"/>
     </row>
     <row r="75" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="92" t="s">
+      <c r="A75" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B75" s="51"/>
-      <c r="C75" s="51"/>
-      <c r="D75" s="51"/>
-      <c r="E75" s="51"/>
-      <c r="F75" s="52"/>
+      <c r="B75" s="53"/>
+      <c r="C75" s="53"/>
+      <c r="D75" s="53"/>
+      <c r="E75" s="53"/>
+      <c r="F75" s="54"/>
       <c r="G75" s="37"/>
       <c r="H75" s="37"/>
       <c r="I75" s="37"/>
@@ -12900,11 +12927,11 @@
       <c r="N75" s="25"/>
     </row>
     <row r="76" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="90" t="s">
-        <v>642</v>
+      <c r="A76" s="93" t="s">
+        <v>634</v>
       </c>
       <c r="B76" s="43" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C76" s="44" t="s">
         <v>14</v>
@@ -12922,12 +12949,12 @@
       <c r="N76" s="25"/>
     </row>
     <row r="77" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="90"/>
+      <c r="A77" s="93"/>
       <c r="B77" s="38" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C77" s="45" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -12942,9 +12969,9 @@
       <c r="N77" s="25"/>
     </row>
     <row r="78" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="90"/>
+      <c r="A78" s="93"/>
       <c r="B78" s="43" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C78" s="44" t="s">
         <v>43</v>
@@ -12962,7 +12989,7 @@
       <c r="N78" s="25"/>
     </row>
     <row r="79" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="90"/>
+      <c r="A79" s="93"/>
       <c r="B79" s="43" t="s">
         <v>195</v>
       </c>
@@ -12982,7 +13009,7 @@
       <c r="N79" s="25"/>
     </row>
     <row r="80" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="90"/>
+      <c r="A80" s="93"/>
       <c r="B80" s="43" t="s">
         <v>187</v>
       </c>
@@ -13002,7 +13029,7 @@
       <c r="N80" s="25"/>
     </row>
     <row r="81" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="90"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="43" t="s">
         <v>201</v>
       </c>
@@ -13022,14 +13049,14 @@
       <c r="N81" s="25"/>
     </row>
     <row r="82" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="92" t="s">
+      <c r="A82" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B82" s="51"/>
-      <c r="C82" s="51"/>
-      <c r="D82" s="51"/>
-      <c r="E82" s="51"/>
-      <c r="F82" s="52"/>
+      <c r="B82" s="53"/>
+      <c r="C82" s="53"/>
+      <c r="D82" s="53"/>
+      <c r="E82" s="53"/>
+      <c r="F82" s="54"/>
       <c r="G82" s="37"/>
       <c r="H82" s="37"/>
       <c r="I82" s="37"/>
@@ -13040,14 +13067,14 @@
       <c r="N82" s="25"/>
     </row>
     <row r="83" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="90" t="s">
-        <v>643</v>
+      <c r="A83" s="93" t="s">
+        <v>635</v>
       </c>
       <c r="B83" s="43" t="s">
         <v>173</v>
       </c>
       <c r="C83" s="44" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
@@ -13062,12 +13089,12 @@
       <c r="N83" s="25"/>
     </row>
     <row r="84" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="90"/>
+      <c r="A84" s="93"/>
       <c r="B84" s="43" t="s">
         <v>176</v>
       </c>
       <c r="C84" s="44" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -13082,12 +13109,12 @@
       <c r="N84" s="25"/>
     </row>
     <row r="85" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="90"/>
+      <c r="A85" s="93"/>
       <c r="B85" s="43" t="s">
         <v>197</v>
       </c>
       <c r="C85" s="44" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
@@ -13102,12 +13129,12 @@
       <c r="N85" s="25"/>
     </row>
     <row r="86" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="90"/>
+      <c r="A86" s="93"/>
       <c r="B86" s="43" t="s">
         <v>180</v>
       </c>
       <c r="C86" s="44" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -13122,14 +13149,14 @@
       <c r="N86" s="25"/>
     </row>
     <row r="87" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="92" t="s">
+      <c r="A87" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B87" s="51"/>
-      <c r="C87" s="51"/>
-      <c r="D87" s="51"/>
-      <c r="E87" s="51"/>
-      <c r="F87" s="52"/>
+      <c r="B87" s="53"/>
+      <c r="C87" s="53"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="54"/>
       <c r="G87" s="37"/>
       <c r="H87" s="37"/>
       <c r="I87" s="37"/>
@@ -13140,11 +13167,11 @@
       <c r="N87" s="25"/>
     </row>
     <row r="88" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="90" t="s">
-        <v>644</v>
+      <c r="A88" s="93" t="s">
+        <v>636</v>
       </c>
       <c r="B88" s="28" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>11</v>
@@ -13162,9 +13189,9 @@
       <c r="N88" s="25"/>
     </row>
     <row r="89" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="90"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>99</v>
@@ -13182,9 +13209,9 @@
       <c r="N89" s="25"/>
     </row>
     <row r="90" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="90"/>
+      <c r="A90" s="93"/>
       <c r="B90" s="28" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>145</v>
@@ -13202,9 +13229,9 @@
       <c r="N90" s="25"/>
     </row>
     <row r="91" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="90"/>
+      <c r="A91" s="93"/>
       <c r="B91" s="28" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>9</v>
@@ -13222,9 +13249,9 @@
       <c r="N91" s="25"/>
     </row>
     <row r="92" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="90"/>
+      <c r="A92" s="93"/>
       <c r="B92" s="28" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>15</v>
@@ -13242,9 +13269,9 @@
       <c r="N92" s="25"/>
     </row>
     <row r="93" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="90"/>
+      <c r="A93" s="93"/>
       <c r="B93" s="28" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>41</v>
@@ -13262,14 +13289,14 @@
       <c r="N93" s="25"/>
     </row>
     <row r="94" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="92" t="s">
+      <c r="A94" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B94" s="51"/>
-      <c r="C94" s="51"/>
-      <c r="D94" s="51"/>
-      <c r="E94" s="51"/>
-      <c r="F94" s="52"/>
+      <c r="B94" s="53"/>
+      <c r="C94" s="53"/>
+      <c r="D94" s="53"/>
+      <c r="E94" s="53"/>
+      <c r="F94" s="54"/>
       <c r="G94" s="37"/>
       <c r="H94" s="37"/>
       <c r="I94" s="37"/>
@@ -13280,11 +13307,11 @@
       <c r="N94" s="25"/>
     </row>
     <row r="95" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="90" t="s">
-        <v>645</v>
+      <c r="A95" s="93" t="s">
+        <v>637</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>93</v>
@@ -13302,9 +13329,9 @@
       <c r="N95" s="25"/>
     </row>
     <row r="96" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="90"/>
+      <c r="A96" s="93"/>
       <c r="B96" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>110</v>
@@ -13322,11 +13349,11 @@
       <c r="N96" s="25"/>
     </row>
     <row r="97" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="90" t="s">
-        <v>646</v>
+      <c r="A97" s="93" t="s">
+        <v>638</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>93</v>
@@ -13344,9 +13371,9 @@
       <c r="N97" s="25"/>
     </row>
     <row r="98" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="91"/>
+      <c r="A98" s="92"/>
       <c r="B98" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>110</v>
@@ -13364,14 +13391,14 @@
       <c r="N98" s="25"/>
     </row>
     <row r="99" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="92" t="s">
+      <c r="A99" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B99" s="51"/>
-      <c r="C99" s="51"/>
-      <c r="D99" s="51"/>
-      <c r="E99" s="51"/>
-      <c r="F99" s="52"/>
+      <c r="B99" s="53"/>
+      <c r="C99" s="53"/>
+      <c r="D99" s="53"/>
+      <c r="E99" s="53"/>
+      <c r="F99" s="54"/>
       <c r="G99" s="37"/>
       <c r="H99" s="37"/>
       <c r="I99" s="37"/>
@@ -13382,14 +13409,14 @@
       <c r="N99" s="25"/>
     </row>
     <row r="100" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="90" t="s">
-        <v>648</v>
+      <c r="A100" s="93" t="s">
+        <v>640</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
@@ -13404,12 +13431,12 @@
       <c r="N100" s="25"/>
     </row>
     <row r="101" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="91"/>
+      <c r="A101" s="92"/>
       <c r="B101" s="15" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -13424,12 +13451,12 @@
       <c r="N101" s="25"/>
     </row>
     <row r="102" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="91"/>
+      <c r="A102" s="92"/>
       <c r="B102" s="15" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -13444,12 +13471,12 @@
       <c r="N102" s="25"/>
     </row>
     <row r="103" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="91"/>
+      <c r="A103" s="92"/>
       <c r="B103" s="15" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
@@ -13464,12 +13491,12 @@
       <c r="N103" s="25"/>
     </row>
     <row r="104" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="91"/>
+      <c r="A104" s="92"/>
       <c r="B104" s="15" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
@@ -13484,12 +13511,12 @@
       <c r="N104" s="25"/>
     </row>
     <row r="105" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="91"/>
+      <c r="A105" s="92"/>
       <c r="B105" s="15" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
@@ -13504,12 +13531,12 @@
       <c r="N105" s="25"/>
     </row>
     <row r="106" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="91"/>
+      <c r="A106" s="92"/>
       <c r="B106" s="15" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
@@ -13524,12 +13551,12 @@
       <c r="N106" s="25"/>
     </row>
     <row r="107" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="91"/>
+      <c r="A107" s="92"/>
       <c r="B107" s="15" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
@@ -13544,12 +13571,12 @@
       <c r="N107" s="25"/>
     </row>
     <row r="108" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="91"/>
+      <c r="A108" s="92"/>
       <c r="B108" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
@@ -13564,9 +13591,9 @@
       <c r="N108" s="25"/>
     </row>
     <row r="109" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="91"/>
+      <c r="A109" s="92"/>
       <c r="B109" s="15" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>80</v>
@@ -13584,9 +13611,9 @@
       <c r="N109" s="25"/>
     </row>
     <row r="110" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="91"/>
+      <c r="A110" s="92"/>
       <c r="B110" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>59</v>
@@ -13604,9 +13631,9 @@
       <c r="N110" s="25"/>
     </row>
     <row r="111" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="91"/>
+      <c r="A111" s="92"/>
       <c r="B111" s="15" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>79</v>
@@ -13624,9 +13651,9 @@
       <c r="N111" s="25"/>
     </row>
     <row r="112" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="91"/>
+      <c r="A112" s="92"/>
       <c r="B112" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>168</v>
@@ -13644,9 +13671,9 @@
       <c r="N112" s="25"/>
     </row>
     <row r="113" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="91"/>
+      <c r="A113" s="92"/>
       <c r="B113" s="15" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>69</v>
@@ -13664,9 +13691,9 @@
       <c r="N113" s="25"/>
     </row>
     <row r="114" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="91"/>
+      <c r="A114" s="92"/>
       <c r="B114" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>72</v>
@@ -13684,11 +13711,11 @@
       <c r="N114" s="25"/>
     </row>
     <row r="115" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="90" t="s">
-        <v>649</v>
+      <c r="A115" s="93" t="s">
+        <v>641</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>81</v>
@@ -13706,9 +13733,9 @@
       <c r="N115" s="25"/>
     </row>
     <row r="116" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="91"/>
+      <c r="A116" s="92"/>
       <c r="B116" s="15" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>83</v>
@@ -13726,9 +13753,9 @@
       <c r="N116" s="25"/>
     </row>
     <row r="117" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="91"/>
+      <c r="A117" s="92"/>
       <c r="B117" s="15" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>80</v>
@@ -13746,9 +13773,9 @@
       <c r="N117" s="25"/>
     </row>
     <row r="118" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="91"/>
+      <c r="A118" s="92"/>
       <c r="B118" s="15" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>79</v>
@@ -13766,9 +13793,9 @@
       <c r="N118" s="25"/>
     </row>
     <row r="119" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="91"/>
+      <c r="A119" s="92"/>
       <c r="B119" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>75</v>
@@ -13786,12 +13813,12 @@
       <c r="N119" s="25"/>
     </row>
     <row r="120" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="91"/>
+      <c r="A120" s="92"/>
       <c r="B120" s="15" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
@@ -13806,9 +13833,9 @@
       <c r="N120" s="25"/>
     </row>
     <row r="121" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="91"/>
+      <c r="A121" s="92"/>
       <c r="B121" s="15" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>168</v>
@@ -13826,9 +13853,9 @@
       <c r="N121" s="25"/>
     </row>
     <row r="122" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="91"/>
+      <c r="A122" s="92"/>
       <c r="B122" s="15" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>69</v>
@@ -13846,9 +13873,9 @@
       <c r="N122" s="25"/>
     </row>
     <row r="123" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="91"/>
+      <c r="A123" s="92"/>
       <c r="B123" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>72</v>
@@ -13866,11 +13893,11 @@
       <c r="N123" s="25"/>
     </row>
     <row r="124" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="90" t="s">
-        <v>650</v>
+      <c r="A124" s="93" t="s">
+        <v>642</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>56</v>
@@ -13888,12 +13915,12 @@
       <c r="N124" s="25"/>
     </row>
     <row r="125" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="91"/>
+      <c r="A125" s="92"/>
       <c r="B125" s="15" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
@@ -13908,9 +13935,9 @@
       <c r="N125" s="25"/>
     </row>
     <row r="126" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="91"/>
+      <c r="A126" s="92"/>
       <c r="B126" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>78</v>
@@ -13928,12 +13955,12 @@
       <c r="N126" s="25"/>
     </row>
     <row r="127" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="91"/>
+      <c r="A127" s="92"/>
       <c r="B127" s="15" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
@@ -13948,9 +13975,9 @@
       <c r="N127" s="25"/>
     </row>
     <row r="128" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="91"/>
+      <c r="A128" s="92"/>
       <c r="B128" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>77</v>
@@ -13968,12 +13995,12 @@
       <c r="N128" s="25"/>
     </row>
     <row r="129" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="91"/>
+      <c r="A129" s="92"/>
       <c r="B129" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
@@ -13988,9 +14015,9 @@
       <c r="N129" s="25"/>
     </row>
     <row r="130" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="91"/>
+      <c r="A130" s="92"/>
       <c r="B130" s="15" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>70</v>
@@ -14008,12 +14035,12 @@
       <c r="N130" s="25"/>
     </row>
     <row r="131" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="91"/>
+      <c r="A131" s="92"/>
       <c r="B131" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
@@ -14028,9 +14055,9 @@
       <c r="N131" s="25"/>
     </row>
     <row r="132" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="91"/>
+      <c r="A132" s="92"/>
       <c r="B132" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>57</v>
@@ -14048,12 +14075,12 @@
       <c r="N132" s="25"/>
     </row>
     <row r="133" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="91"/>
+      <c r="A133" s="92"/>
       <c r="B133" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
@@ -14068,9 +14095,9 @@
       <c r="N133" s="25"/>
     </row>
     <row r="134" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="91"/>
+      <c r="A134" s="92"/>
       <c r="B134" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>63</v>
@@ -14088,12 +14115,12 @@
       <c r="N134" s="25"/>
     </row>
     <row r="135" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="91"/>
+      <c r="A135" s="92"/>
       <c r="B135" s="15" t="s">
         <v>210</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
@@ -14108,11 +14135,11 @@
       <c r="N135" s="25"/>
     </row>
     <row r="136" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="90" t="s">
-        <v>651</v>
+      <c r="A136" s="93" t="s">
+        <v>643</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>56</v>
@@ -14130,7 +14157,7 @@
       <c r="N136" s="25"/>
     </row>
     <row r="137" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="91"/>
+      <c r="A137" s="92"/>
       <c r="B137" s="15" t="s">
         <v>209</v>
       </c>
@@ -14150,9 +14177,9 @@
       <c r="N137" s="25"/>
     </row>
     <row r="138" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="91"/>
+      <c r="A138" s="92"/>
       <c r="B138" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>77</v>
@@ -14170,9 +14197,9 @@
       <c r="N138" s="25"/>
     </row>
     <row r="139" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="91"/>
+      <c r="A139" s="92"/>
       <c r="B139" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>58</v>
@@ -14190,9 +14217,9 @@
       <c r="N139" s="25"/>
     </row>
     <row r="140" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="91"/>
+      <c r="A140" s="92"/>
       <c r="B140" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>70</v>
@@ -14210,9 +14237,9 @@
       <c r="N140" s="25"/>
     </row>
     <row r="141" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="91"/>
+      <c r="A141" s="92"/>
       <c r="B141" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>57</v>
@@ -14230,9 +14257,9 @@
       <c r="N141" s="25"/>
     </row>
     <row r="142" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="91"/>
+      <c r="A142" s="92"/>
       <c r="B142" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>63</v>
@@ -14251,10 +14278,10 @@
     </row>
     <row r="143" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="17" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="B143" s="15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>69</v>
@@ -14272,11 +14299,11 @@
       <c r="N143" s="25"/>
     </row>
     <row r="144" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="90" t="s">
-        <v>653</v>
+      <c r="A144" s="93" t="s">
+        <v>645</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>81</v>
@@ -14294,9 +14321,9 @@
       <c r="N144" s="25"/>
     </row>
     <row r="145" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="91"/>
+      <c r="A145" s="92"/>
       <c r="B145" s="15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>75</v>
@@ -14314,9 +14341,9 @@
       <c r="N145" s="25"/>
     </row>
     <row r="146" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="91"/>
+      <c r="A146" s="92"/>
       <c r="B146" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>80</v>
@@ -14334,9 +14361,9 @@
       <c r="N146" s="25"/>
     </row>
     <row r="147" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="91"/>
+      <c r="A147" s="92"/>
       <c r="B147" s="15" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>79</v>
@@ -14354,9 +14381,9 @@
       <c r="N147" s="25"/>
     </row>
     <row r="148" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="91"/>
+      <c r="A148" s="92"/>
       <c r="B148" s="15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>69</v>
@@ -14374,14 +14401,14 @@
       <c r="N148" s="25"/>
     </row>
     <row r="149" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="92" t="s">
+      <c r="A149" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B149" s="51"/>
-      <c r="C149" s="51"/>
-      <c r="D149" s="51"/>
-      <c r="E149" s="51"/>
-      <c r="F149" s="52"/>
+      <c r="B149" s="53"/>
+      <c r="C149" s="53"/>
+      <c r="D149" s="53"/>
+      <c r="E149" s="53"/>
+      <c r="F149" s="54"/>
       <c r="G149" s="37"/>
       <c r="H149" s="37"/>
       <c r="I149" s="37"/>
@@ -14392,11 +14419,11 @@
       <c r="N149" s="25"/>
     </row>
     <row r="150" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="90" t="s">
-        <v>655</v>
+      <c r="A150" s="93" t="s">
+        <v>647</v>
       </c>
       <c r="B150" s="28" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>30</v>
@@ -14414,9 +14441,9 @@
       <c r="N150" s="25"/>
     </row>
     <row r="151" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="90"/>
+      <c r="A151" s="93"/>
       <c r="B151" s="28" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>42</v>
@@ -14434,9 +14461,9 @@
       <c r="N151" s="25"/>
     </row>
     <row r="152" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="90"/>
+      <c r="A152" s="93"/>
       <c r="B152" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>21</v>
@@ -14454,9 +14481,9 @@
       <c r="N152" s="25"/>
     </row>
     <row r="153" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="90"/>
+      <c r="A153" s="93"/>
       <c r="B153" s="28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>28</v>
@@ -14474,9 +14501,9 @@
       <c r="N153" s="25"/>
     </row>
     <row r="154" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="90"/>
+      <c r="A154" s="93"/>
       <c r="B154" s="28" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>5</v>
@@ -14494,9 +14521,9 @@
       <c r="N154" s="25"/>
     </row>
     <row r="155" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="90"/>
+      <c r="A155" s="93"/>
       <c r="B155" s="28" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>19</v>
@@ -14514,11 +14541,11 @@
       <c r="N155" s="25"/>
     </row>
     <row r="156" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="90" t="s">
-        <v>656</v>
+      <c r="A156" s="93" t="s">
+        <v>648</v>
       </c>
       <c r="B156" s="28" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>32</v>
@@ -14536,9 +14563,9 @@
       <c r="N156" s="25"/>
     </row>
     <row r="157" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="90"/>
+      <c r="A157" s="93"/>
       <c r="B157" s="28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>10</v>
@@ -14556,9 +14583,9 @@
       <c r="N157" s="25"/>
     </row>
     <row r="158" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="90"/>
+      <c r="A158" s="93"/>
       <c r="B158" s="28" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>25</v>
@@ -14576,9 +14603,9 @@
       <c r="N158" s="25"/>
     </row>
     <row r="159" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="90"/>
+      <c r="A159" s="93"/>
       <c r="B159" s="28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>16</v>
@@ -14596,9 +14623,9 @@
       <c r="N159" s="25"/>
     </row>
     <row r="160" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="90"/>
+      <c r="A160" s="93"/>
       <c r="B160" s="28" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>55</v>
@@ -14616,9 +14643,9 @@
       <c r="N160" s="25"/>
     </row>
     <row r="161" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="90"/>
+      <c r="A161" s="93"/>
       <c r="B161" s="28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>20</v>
@@ -14636,14 +14663,14 @@
       <c r="N161" s="25"/>
     </row>
     <row r="162" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="90" t="s">
-        <v>657</v>
+      <c r="A162" s="93" t="s">
+        <v>649</v>
       </c>
       <c r="B162" s="28" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
@@ -14658,12 +14685,12 @@
       <c r="N162" s="25"/>
     </row>
     <row r="163" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="90"/>
+      <c r="A163" s="93"/>
       <c r="B163" s="28" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
@@ -14678,14 +14705,14 @@
       <c r="N163" s="25"/>
     </row>
     <row r="164" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="92" t="s">
-        <v>507</v>
-      </c>
-      <c r="B164" s="51"/>
-      <c r="C164" s="51"/>
-      <c r="D164" s="51"/>
-      <c r="E164" s="51"/>
-      <c r="F164" s="52"/>
+      <c r="A164" s="94" t="s">
+        <v>505</v>
+      </c>
+      <c r="B164" s="53"/>
+      <c r="C164" s="53"/>
+      <c r="D164" s="53"/>
+      <c r="E164" s="53"/>
+      <c r="F164" s="54"/>
       <c r="G164" s="37"/>
       <c r="H164" s="37"/>
       <c r="I164" s="37"/>
@@ -14696,11 +14723,11 @@
       <c r="N164" s="25"/>
     </row>
     <row r="165" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="91" t="s">
-        <v>214</v>
+      <c r="A165" s="101" t="s">
+        <v>735</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>135</v>
@@ -14718,12 +14745,12 @@
       <c r="N165" s="25"/>
     </row>
     <row r="166" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="91"/>
+      <c r="A166" s="102"/>
       <c r="B166" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
@@ -14738,12 +14765,12 @@
       <c r="N166" s="25"/>
     </row>
     <row r="167" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="91"/>
+      <c r="A167" s="102"/>
       <c r="B167" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
@@ -14758,14 +14785,10 @@
       <c r="N167" s="25"/>
     </row>
     <row r="168" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="91" t="s">
-        <v>673</v>
-      </c>
-      <c r="B168" s="15" t="s">
-        <v>417</v>
-      </c>
+      <c r="A168" s="102"/>
+      <c r="B168" s="15"/>
       <c r="C168" s="4" t="s">
-        <v>559</v>
+        <v>746</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
@@ -14780,12 +14803,10 @@
       <c r="N168" s="25"/>
     </row>
     <row r="169" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="91"/>
-      <c r="B169" s="15" t="s">
-        <v>381</v>
-      </c>
+      <c r="A169" s="103"/>
+      <c r="B169" s="15"/>
       <c r="C169" s="4" t="s">
-        <v>562</v>
+        <v>747</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
@@ -14800,14 +14821,14 @@
       <c r="N169" s="25"/>
     </row>
     <row r="170" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="91" t="s">
-        <v>672</v>
+      <c r="A170" s="92" t="s">
+        <v>658</v>
       </c>
       <c r="B170" s="15" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>666</v>
+        <v>556</v>
       </c>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
@@ -14822,12 +14843,12 @@
       <c r="N170" s="25"/>
     </row>
     <row r="171" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="91"/>
+      <c r="A171" s="92"/>
       <c r="B171" s="15" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>667</v>
+        <v>559</v>
       </c>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
@@ -14842,14 +14863,14 @@
       <c r="N171" s="25"/>
     </row>
     <row r="172" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="91" t="s">
-        <v>671</v>
+      <c r="A172" s="92" t="s">
+        <v>657</v>
       </c>
       <c r="B172" s="15" t="s">
-        <v>244</v>
+        <v>397</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>82</v>
+        <v>653</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
@@ -14864,12 +14885,12 @@
       <c r="N172" s="25"/>
     </row>
     <row r="173" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="91"/>
+      <c r="A173" s="92"/>
       <c r="B173" s="15" t="s">
-        <v>324</v>
+        <v>363</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>610</v>
+        <v>654</v>
       </c>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
@@ -14884,14 +14905,14 @@
       <c r="N173" s="25"/>
     </row>
     <row r="174" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="91" t="s">
-        <v>670</v>
+      <c r="A174" s="92" t="s">
+        <v>736</v>
       </c>
       <c r="B174" s="15" t="s">
-        <v>603</v>
+        <v>243</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>658</v>
+        <v>82</v>
       </c>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
@@ -14906,12 +14927,12 @@
       <c r="N174" s="25"/>
     </row>
     <row r="175" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="91"/>
+      <c r="A175" s="92"/>
       <c r="B175" s="15" t="s">
-        <v>604</v>
+        <v>322</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>659</v>
+        <v>602</v>
       </c>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
@@ -14926,12 +14947,14 @@
       <c r="N175" s="25"/>
     </row>
     <row r="176" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="91"/>
+      <c r="A176" s="17" t="s">
+        <v>656</v>
+      </c>
       <c r="B176" s="15" t="s">
-        <v>605</v>
+        <v>303</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>660</v>
+        <v>84</v>
       </c>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
@@ -14946,12 +14969,14 @@
       <c r="N176" s="25"/>
     </row>
     <row r="177" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="91"/>
+      <c r="A177" s="92" t="s">
+        <v>655</v>
+      </c>
       <c r="B177" s="15" t="s">
-        <v>606</v>
+        <v>292</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
@@ -14966,12 +14991,12 @@
       <c r="N177" s="25"/>
     </row>
     <row r="178" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="91"/>
+      <c r="A178" s="92"/>
       <c r="B178" s="15" t="s">
-        <v>607</v>
+        <v>254</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
@@ -14986,14 +15011,12 @@
       <c r="N178" s="25"/>
     </row>
     <row r="179" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="91" t="s">
-        <v>669</v>
-      </c>
+      <c r="A179" s="92"/>
       <c r="B179" s="15" t="s">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>84</v>
+        <v>652</v>
       </c>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
@@ -15008,34 +15031,32 @@
       <c r="N179" s="25"/>
     </row>
     <row r="180" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="91"/>
-      <c r="B180" s="15" t="s">
-        <v>300</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="D180" s="4"/>
-      <c r="E180" s="4"/>
-      <c r="F180" s="16"/>
-      <c r="G180" s="14"/>
-      <c r="H180" s="14"/>
-      <c r="I180" s="14"/>
-      <c r="J180" s="14"/>
-      <c r="K180" s="14"/>
-      <c r="L180" s="14"/>
-      <c r="M180" s="14"/>
+      <c r="A180" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="B180" s="53"/>
+      <c r="C180" s="53"/>
+      <c r="D180" s="53"/>
+      <c r="E180" s="53"/>
+      <c r="F180" s="54"/>
+      <c r="G180" s="37"/>
+      <c r="H180" s="37"/>
+      <c r="I180" s="37"/>
+      <c r="J180" s="37"/>
+      <c r="K180" s="37"/>
+      <c r="L180" s="37"/>
+      <c r="M180" s="37"/>
       <c r="N180" s="25"/>
     </row>
     <row r="181" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="91" t="s">
-        <v>668</v>
+      <c r="A181" s="92" t="s">
+        <v>665</v>
       </c>
       <c r="B181" s="15" t="s">
-        <v>293</v>
+        <v>206</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>663</v>
+        <v>215</v>
       </c>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
@@ -15050,12 +15071,12 @@
       <c r="N181" s="25"/>
     </row>
     <row r="182" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="91"/>
+      <c r="A182" s="92"/>
       <c r="B182" s="15" t="s">
-        <v>255</v>
+        <v>462</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>664</v>
+        <v>444</v>
       </c>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
@@ -15070,12 +15091,14 @@
       <c r="N182" s="25"/>
     </row>
     <row r="183" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="91"/>
+      <c r="A183" s="92" t="s">
+        <v>666</v>
+      </c>
       <c r="B183" s="15" t="s">
-        <v>274</v>
+        <v>469</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>665</v>
+        <v>46</v>
       </c>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
@@ -15090,32 +15113,32 @@
       <c r="N183" s="25"/>
     </row>
     <row r="184" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="92" t="s">
-        <v>114</v>
-      </c>
-      <c r="B184" s="51"/>
-      <c r="C184" s="51"/>
-      <c r="D184" s="51"/>
-      <c r="E184" s="51"/>
-      <c r="F184" s="52"/>
-      <c r="G184" s="37"/>
-      <c r="H184" s="37"/>
-      <c r="I184" s="37"/>
-      <c r="J184" s="37"/>
-      <c r="K184" s="37"/>
-      <c r="L184" s="37"/>
-      <c r="M184" s="37"/>
+      <c r="A184" s="92"/>
+      <c r="B184" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D184" s="4"/>
+      <c r="E184" s="4"/>
+      <c r="F184" s="16"/>
+      <c r="G184" s="14"/>
+      <c r="H184" s="14"/>
+      <c r="I184" s="14"/>
+      <c r="J184" s="14"/>
+      <c r="K184" s="14"/>
+      <c r="L184" s="14"/>
+      <c r="M184" s="14"/>
       <c r="N184" s="25"/>
     </row>
     <row r="185" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="91" t="s">
-        <v>680</v>
-      </c>
+      <c r="A185" s="92"/>
       <c r="B185" s="15" t="s">
-        <v>206</v>
+        <v>456</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
@@ -15130,12 +15153,12 @@
       <c r="N185" s="25"/>
     </row>
     <row r="186" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="91"/>
+      <c r="A186" s="92"/>
       <c r="B186" s="15" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>446</v>
+        <v>3</v>
       </c>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
@@ -15150,14 +15173,12 @@
       <c r="N186" s="25"/>
     </row>
     <row r="187" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="91" t="s">
-        <v>681</v>
-      </c>
+      <c r="A187" s="92"/>
       <c r="B187" s="15" t="s">
-        <v>471</v>
+        <v>443</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
@@ -15172,12 +15193,12 @@
       <c r="N187" s="25"/>
     </row>
     <row r="188" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="91"/>
+      <c r="A188" s="92"/>
       <c r="B188" s="15" t="s">
         <v>454</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
@@ -15192,12 +15213,14 @@
       <c r="N188" s="25"/>
     </row>
     <row r="189" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="91"/>
+      <c r="A189" s="92" t="s">
+        <v>615</v>
+      </c>
       <c r="B189" s="15" t="s">
-        <v>458</v>
+        <v>659</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>24</v>
+        <v>660</v>
       </c>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
@@ -15212,12 +15235,12 @@
       <c r="N189" s="25"/>
     </row>
     <row r="190" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="91"/>
+      <c r="A190" s="92"/>
       <c r="B190" s="15" t="s">
-        <v>462</v>
+        <v>661</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>3</v>
+        <v>662</v>
       </c>
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
@@ -15232,12 +15255,12 @@
       <c r="N190" s="25"/>
     </row>
     <row r="191" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="91"/>
+      <c r="A191" s="92"/>
       <c r="B191" s="15" t="s">
-        <v>445</v>
+        <v>663</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>1</v>
+        <v>664</v>
       </c>
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
@@ -15252,12 +15275,14 @@
       <c r="N191" s="25"/>
     </row>
     <row r="192" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="91"/>
-      <c r="B192" s="15" t="s">
-        <v>456</v>
-      </c>
-      <c r="C192" s="4" t="s">
-        <v>6</v>
+      <c r="A192" s="97" t="s">
+        <v>737</v>
+      </c>
+      <c r="B192" s="99" t="s">
+        <v>738</v>
+      </c>
+      <c r="C192" s="100" t="s">
+        <v>739</v>
       </c>
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
@@ -15272,14 +15297,12 @@
       <c r="N192" s="25"/>
     </row>
     <row r="193" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="91" t="s">
-        <v>623</v>
-      </c>
-      <c r="B193" s="15" t="s">
-        <v>674</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>675</v>
+      <c r="A193" s="98"/>
+      <c r="B193" s="99" t="s">
+        <v>740</v>
+      </c>
+      <c r="C193" s="100" t="s">
+        <v>741</v>
       </c>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
@@ -15294,12 +15317,12 @@
       <c r="N193" s="25"/>
     </row>
     <row r="194" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="91"/>
-      <c r="B194" s="15" t="s">
-        <v>676</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>677</v>
+      <c r="A194" s="98"/>
+      <c r="B194" s="99" t="s">
+        <v>742</v>
+      </c>
+      <c r="C194" s="100" t="s">
+        <v>743</v>
       </c>
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
@@ -15314,12 +15337,12 @@
       <c r="N194" s="25"/>
     </row>
     <row r="195" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="91"/>
-      <c r="B195" s="15" t="s">
-        <v>678</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>679</v>
+      <c r="A195" s="98"/>
+      <c r="B195" s="99" t="s">
+        <v>744</v>
+      </c>
+      <c r="C195" s="100" t="s">
+        <v>745</v>
       </c>
       <c r="D195" s="4"/>
       <c r="E195" s="4"/>
@@ -15334,14 +15357,14 @@
       <c r="N195" s="25"/>
     </row>
     <row r="196" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A196" s="93" t="s">
+      <c r="A196" s="96" t="s">
         <v>114</v>
       </c>
-      <c r="B196" s="54"/>
-      <c r="C196" s="54"/>
-      <c r="D196" s="54"/>
-      <c r="E196" s="54"/>
-      <c r="F196" s="55"/>
+      <c r="B196" s="87"/>
+      <c r="C196" s="87"/>
+      <c r="D196" s="87"/>
+      <c r="E196" s="87"/>
+      <c r="F196" s="88"/>
       <c r="G196" s="46"/>
       <c r="H196" s="46"/>
       <c r="I196" s="46"/>
@@ -15352,14 +15375,14 @@
       <c r="N196" s="27"/>
     </row>
     <row r="197" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A197" s="56" t="s">
+      <c r="A197" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="B197" s="57"/>
-      <c r="C197" s="57"/>
-      <c r="D197" s="57"/>
-      <c r="E197" s="57"/>
-      <c r="F197" s="58"/>
+      <c r="B197" s="90"/>
+      <c r="C197" s="90"/>
+      <c r="D197" s="90"/>
+      <c r="E197" s="90"/>
+      <c r="F197" s="91"/>
       <c r="G197" s="47"/>
       <c r="H197" s="47"/>
       <c r="I197" s="47"/>
@@ -15402,7 +15425,50 @@
       <c r="N199" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="58">
+    <mergeCell ref="A192:A195"/>
+    <mergeCell ref="A165:A169"/>
+    <mergeCell ref="A48:A58"/>
+    <mergeCell ref="A60:A74"/>
+    <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="A88:A93"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A124:A135"/>
+    <mergeCell ref="A136:A142"/>
+    <mergeCell ref="A144:A148"/>
+    <mergeCell ref="A115:A123"/>
+    <mergeCell ref="A100:A114"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A177:A179"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A8:A19"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A197:F197"/>
+    <mergeCell ref="A196:F196"/>
+    <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A164:F164"/>
+    <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A181:A182"/>
+    <mergeCell ref="A183:A188"/>
+    <mergeCell ref="A189:A191"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A150:A155"/>
+    <mergeCell ref="A156:A161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A21:A28"/>
+    <mergeCell ref="A35:A46"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A30:A33"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
@@ -15418,50 +15484,6 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="A21:A28"/>
-    <mergeCell ref="A35:A46"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A8:A19"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A197:F197"/>
-    <mergeCell ref="A196:F196"/>
-    <mergeCell ref="A184:F184"/>
-    <mergeCell ref="A164:F164"/>
-    <mergeCell ref="A149:F149"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="A187:A192"/>
-    <mergeCell ref="A193:A195"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A150:A155"/>
-    <mergeCell ref="A156:A161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A174:A178"/>
-    <mergeCell ref="A179:A180"/>
-    <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A181:A183"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A87:F87"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="A124:A135"/>
-    <mergeCell ref="A136:A142"/>
-    <mergeCell ref="A144:A148"/>
-    <mergeCell ref="A115:A123"/>
-    <mergeCell ref="A165:A167"/>
-    <mergeCell ref="A100:A114"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="A48:A58"/>
-    <mergeCell ref="A60:A74"/>
-    <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A75:F75"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17946,20 +17968,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="80"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30"/>
@@ -17975,13 +17997,13 @@
       <c r="K3" s="30"/>
       <c r="L3" s="30"/>
       <c r="M3" s="31" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="N3" s="49"/>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M4" s="36" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="N4" s="49"/>
     </row>
@@ -17990,74 +18012,74 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88" t="s">
-        <v>414</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>624</v>
-      </c>
-      <c r="C6" s="83" t="s">
-        <v>625</v>
-      </c>
-      <c r="D6" s="83" t="s">
-        <v>626</v>
-      </c>
-      <c r="E6" s="83" t="s">
-        <v>627</v>
-      </c>
-      <c r="F6" s="78" t="s">
-        <v>628</v>
-      </c>
-      <c r="G6" s="78" t="s">
-        <v>578</v>
-      </c>
-      <c r="H6" s="78" t="s">
-        <v>582</v>
-      </c>
-      <c r="I6" s="78" t="s">
-        <v>588</v>
-      </c>
-      <c r="J6" s="78" t="s">
-        <v>589</v>
-      </c>
-      <c r="K6" s="78" t="s">
-        <v>590</v>
-      </c>
-      <c r="L6" s="78" t="s">
-        <v>608</v>
-      </c>
-      <c r="M6" s="78" t="s">
-        <v>629</v>
-      </c>
-      <c r="N6" s="81" t="s">
-        <v>630</v>
+      <c r="A6" s="64" t="s">
+        <v>412</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>616</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>617</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>618</v>
+      </c>
+      <c r="E6" s="59" t="s">
+        <v>619</v>
+      </c>
+      <c r="F6" s="55" t="s">
+        <v>620</v>
+      </c>
+      <c r="G6" s="55" t="s">
+        <v>575</v>
+      </c>
+      <c r="H6" s="55" t="s">
+        <v>579</v>
+      </c>
+      <c r="I6" s="55" t="s">
+        <v>585</v>
+      </c>
+      <c r="J6" s="55" t="s">
+        <v>586</v>
+      </c>
+      <c r="K6" s="55" t="s">
+        <v>587</v>
+      </c>
+      <c r="L6" s="55" t="s">
+        <v>600</v>
+      </c>
+      <c r="M6" s="55" t="s">
+        <v>621</v>
+      </c>
+      <c r="N6" s="71" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="89"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="84"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="79"/>
-      <c r="K7" s="79"/>
-      <c r="L7" s="79"/>
-      <c r="M7" s="79"/>
-      <c r="N7" s="82"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="72"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="94" t="s">
-        <v>710</v>
-      </c>
-      <c r="B8" s="95" t="s">
-        <v>727</v>
+      <c r="A8" s="95" t="s">
+        <v>695</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>712</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>687</v>
+        <v>672</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -18072,12 +18094,12 @@
       <c r="N8" s="26"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="91"/>
+      <c r="A9" s="92"/>
       <c r="B9" s="28" t="s">
-        <v>728</v>
+        <v>713</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>688</v>
+        <v>673</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -18092,12 +18114,12 @@
       <c r="N9" s="25"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="91"/>
-      <c r="B10" s="96" t="s">
-        <v>729</v>
+      <c r="A10" s="92"/>
+      <c r="B10" s="51" t="s">
+        <v>714</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>689</v>
+        <v>674</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="18"/>
@@ -18112,12 +18134,12 @@
       <c r="N10" s="25"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="91"/>
-      <c r="B11" s="96" t="s">
-        <v>730</v>
+      <c r="A11" s="92"/>
+      <c r="B11" s="51" t="s">
+        <v>715</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>690</v>
+        <v>675</v>
       </c>
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
@@ -18132,12 +18154,12 @@
       <c r="N11" s="25"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="91"/>
-      <c r="B12" s="96" t="s">
-        <v>731</v>
+      <c r="A12" s="92"/>
+      <c r="B12" s="51" t="s">
+        <v>716</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>691</v>
+        <v>676</v>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
@@ -18152,12 +18174,12 @@
       <c r="N12" s="25"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="91"/>
-      <c r="B13" s="96" t="s">
-        <v>732</v>
+      <c r="A13" s="92"/>
+      <c r="B13" s="51" t="s">
+        <v>717</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
@@ -18172,12 +18194,12 @@
       <c r="N13" s="25"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="91"/>
-      <c r="B14" s="96" t="s">
-        <v>733</v>
+      <c r="A14" s="92"/>
+      <c r="B14" s="51" t="s">
+        <v>718</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>693</v>
+        <v>678</v>
       </c>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
@@ -18192,12 +18214,12 @@
       <c r="N14" s="25"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="91"/>
-      <c r="B15" s="96" t="s">
-        <v>734</v>
+      <c r="A15" s="92"/>
+      <c r="B15" s="51" t="s">
+        <v>719</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
@@ -18212,12 +18234,12 @@
       <c r="N15" s="25"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="91"/>
-      <c r="B16" s="96" t="s">
-        <v>735</v>
+      <c r="A16" s="92"/>
+      <c r="B16" s="51" t="s">
+        <v>720</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
@@ -18232,12 +18254,12 @@
       <c r="N16" s="25"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="91"/>
-      <c r="B17" s="96" t="s">
-        <v>736</v>
+      <c r="A17" s="92"/>
+      <c r="B17" s="51" t="s">
+        <v>721</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
@@ -18252,12 +18274,12 @@
       <c r="N17" s="25"/>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="91"/>
-      <c r="B18" s="96" t="s">
-        <v>737</v>
+      <c r="A18" s="92"/>
+      <c r="B18" s="51" t="s">
+        <v>722</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>697</v>
+        <v>682</v>
       </c>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
@@ -18272,12 +18294,12 @@
       <c r="N18" s="25"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="91"/>
-      <c r="B19" s="96" t="s">
-        <v>738</v>
+      <c r="A19" s="92"/>
+      <c r="B19" s="51" t="s">
+        <v>723</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>698</v>
+        <v>683</v>
       </c>
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
@@ -18292,12 +18314,12 @@
       <c r="N19" s="25"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="91"/>
-      <c r="B20" s="96" t="s">
-        <v>739</v>
+      <c r="A20" s="92"/>
+      <c r="B20" s="51" t="s">
+        <v>724</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>699</v>
+        <v>684</v>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="18"/>
@@ -18312,12 +18334,12 @@
       <c r="N20" s="25"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="91"/>
-      <c r="B21" s="96" t="s">
-        <v>740</v>
+      <c r="A21" s="92"/>
+      <c r="B21" s="51" t="s">
+        <v>725</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>700</v>
+        <v>685</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="18"/>
@@ -18332,12 +18354,12 @@
       <c r="N21" s="25"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="91"/>
-      <c r="B22" s="96" t="s">
-        <v>741</v>
+      <c r="A22" s="92"/>
+      <c r="B22" s="51" t="s">
+        <v>726</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>701</v>
+        <v>686</v>
       </c>
       <c r="D22" s="18"/>
       <c r="E22" s="18"/>
@@ -18352,12 +18374,12 @@
       <c r="N22" s="25"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="91"/>
-      <c r="B23" s="96" t="s">
-        <v>742</v>
+      <c r="A23" s="92"/>
+      <c r="B23" s="51" t="s">
+        <v>727</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>702</v>
+        <v>687</v>
       </c>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
@@ -18372,12 +18394,12 @@
       <c r="N23" s="25"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="91"/>
-      <c r="B24" s="96" t="s">
-        <v>743</v>
+      <c r="A24" s="92"/>
+      <c r="B24" s="51" t="s">
+        <v>728</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>703</v>
+        <v>688</v>
       </c>
       <c r="D24" s="18"/>
       <c r="E24" s="18"/>
@@ -18392,12 +18414,12 @@
       <c r="N24" s="25"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="91"/>
-      <c r="B25" s="96" t="s">
-        <v>744</v>
+      <c r="A25" s="92"/>
+      <c r="B25" s="51" t="s">
+        <v>729</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>704</v>
+        <v>689</v>
       </c>
       <c r="D25" s="18"/>
       <c r="E25" s="18"/>
@@ -18412,12 +18434,12 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="91"/>
-      <c r="B26" s="96" t="s">
-        <v>745</v>
+      <c r="A26" s="92"/>
+      <c r="B26" s="51" t="s">
+        <v>730</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>705</v>
+        <v>690</v>
       </c>
       <c r="D26" s="18"/>
       <c r="E26" s="18"/>
@@ -18432,12 +18454,12 @@
       <c r="N26" s="25"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="91"/>
-      <c r="B27" s="96" t="s">
-        <v>746</v>
+      <c r="A27" s="92"/>
+      <c r="B27" s="51" t="s">
+        <v>731</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>706</v>
+        <v>691</v>
       </c>
       <c r="D27" s="18"/>
       <c r="E27" s="18"/>
@@ -18452,12 +18474,12 @@
       <c r="N27" s="25"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="91"/>
-      <c r="B28" s="96" t="s">
-        <v>747</v>
+      <c r="A28" s="92"/>
+      <c r="B28" s="51" t="s">
+        <v>732</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="D28" s="18"/>
       <c r="E28" s="18"/>
@@ -18472,12 +18494,12 @@
       <c r="N28" s="25"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="91"/>
-      <c r="B29" s="96" t="s">
-        <v>748</v>
+      <c r="A29" s="92"/>
+      <c r="B29" s="51" t="s">
+        <v>733</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>708</v>
+        <v>693</v>
       </c>
       <c r="D29" s="18"/>
       <c r="E29" s="18"/>
@@ -18492,12 +18514,12 @@
       <c r="N29" s="25"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="91"/>
-      <c r="B30" s="96" t="s">
-        <v>749</v>
+      <c r="A30" s="92"/>
+      <c r="B30" s="51" t="s">
+        <v>734</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>709</v>
+        <v>694</v>
       </c>
       <c r="D30" s="18"/>
       <c r="E30" s="18"/>
@@ -18512,14 +18534,14 @@
       <c r="N30" s="25"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="92" t="s">
+      <c r="A31" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="54"/>
       <c r="G31" s="37"/>
       <c r="H31" s="37"/>
       <c r="I31" s="37"/>
@@ -18530,11 +18552,11 @@
       <c r="N31" s="25"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="91" t="s">
-        <v>711</v>
+      <c r="A32" s="92" t="s">
+        <v>696</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>96</v>
@@ -18552,9 +18574,9 @@
       <c r="N32" s="25"/>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="91"/>
+      <c r="A33" s="92"/>
       <c r="B33" s="15" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>117</v>
@@ -18572,9 +18594,9 @@
       <c r="N33" s="25"/>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="91"/>
+      <c r="A34" s="92"/>
       <c r="B34" s="15" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>119</v>
@@ -18592,9 +18614,9 @@
       <c r="N34" s="25"/>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="91"/>
+      <c r="A35" s="92"/>
       <c r="B35" s="15" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>115</v>
@@ -18612,9 +18634,9 @@
       <c r="N35" s="25"/>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="91"/>
+      <c r="A36" s="92"/>
       <c r="B36" s="15" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>147</v>
@@ -18632,9 +18654,9 @@
       <c r="N36" s="25"/>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="91"/>
+      <c r="A37" s="92"/>
       <c r="B37" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>146</v>
@@ -18652,9 +18674,9 @@
       <c r="N37" s="25"/>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="91"/>
+      <c r="A38" s="92"/>
       <c r="B38" s="15" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>105</v>
@@ -18672,9 +18694,9 @@
       <c r="N38" s="25"/>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="91"/>
+      <c r="A39" s="92"/>
       <c r="B39" s="15" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>116</v>
@@ -18692,14 +18714,14 @@
       <c r="N39" s="25"/>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="92" t="s">
+      <c r="A40" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B40" s="51"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="52"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="54"/>
       <c r="G40" s="37"/>
       <c r="H40" s="37"/>
       <c r="I40" s="37"/>
@@ -18710,11 +18732,11 @@
       <c r="N40" s="25"/>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="90" t="s">
-        <v>713</v>
+      <c r="A41" s="93" t="s">
+        <v>698</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>61</v>
@@ -18732,9 +18754,9 @@
       <c r="N41" s="25"/>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="90"/>
+      <c r="A42" s="93"/>
       <c r="B42" s="28" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>71</v>
@@ -18752,12 +18774,12 @@
       <c r="N42" s="25"/>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="90"/>
+      <c r="A43" s="93"/>
       <c r="B43" s="28" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>712</v>
+        <v>697</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -18772,12 +18794,12 @@
       <c r="N43" s="25"/>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="90"/>
+      <c r="A44" s="93"/>
       <c r="B44" s="28" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -18792,12 +18814,12 @@
       <c r="N44" s="25"/>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="90"/>
+      <c r="A45" s="93"/>
       <c r="B45" s="28" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -18812,12 +18834,12 @@
       <c r="N45" s="25"/>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="90"/>
+      <c r="A46" s="93"/>
       <c r="B46" s="28" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -18832,12 +18854,12 @@
       <c r="N46" s="25"/>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="90"/>
+      <c r="A47" s="93"/>
       <c r="B47" s="28" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -18852,12 +18874,12 @@
       <c r="N47" s="25"/>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="90"/>
+      <c r="A48" s="93"/>
       <c r="B48" s="28" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -18872,12 +18894,12 @@
       <c r="N48" s="25"/>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="90"/>
+      <c r="A49" s="93"/>
       <c r="B49" s="28" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -18892,14 +18914,14 @@
       <c r="N49" s="25"/>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="92" t="s">
-        <v>507</v>
-      </c>
-      <c r="B50" s="51"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="52"/>
+      <c r="A50" s="94" t="s">
+        <v>505</v>
+      </c>
+      <c r="B50" s="53"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
       <c r="G50" s="37"/>
       <c r="H50" s="37"/>
       <c r="I50" s="37"/>
@@ -18910,11 +18932,11 @@
       <c r="N50" s="25"/>
     </row>
     <row r="51" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="91" t="s">
-        <v>715</v>
+      <c r="A51" s="92" t="s">
+        <v>700</v>
       </c>
       <c r="B51" s="28" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>138</v>
@@ -18932,9 +18954,9 @@
       <c r="N51" s="25"/>
     </row>
     <row r="52" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="91"/>
+      <c r="A52" s="92"/>
       <c r="B52" s="28" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>134</v>
@@ -18952,9 +18974,9 @@
       <c r="N52" s="25"/>
     </row>
     <row r="53" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="91"/>
+      <c r="A53" s="92"/>
       <c r="B53" s="28" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>132</v>
@@ -18972,9 +18994,9 @@
       <c r="N53" s="25"/>
     </row>
     <row r="54" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="91"/>
+      <c r="A54" s="92"/>
       <c r="B54" s="28" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>140</v>
@@ -18992,12 +19014,12 @@
       <c r="N54" s="25"/>
     </row>
     <row r="55" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="91"/>
+      <c r="A55" s="92"/>
       <c r="B55" s="28" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>714</v>
+        <v>699</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -19012,14 +19034,14 @@
       <c r="N55" s="25"/>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="92" t="s">
+      <c r="A56" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B56" s="51"/>
-      <c r="C56" s="51"/>
-      <c r="D56" s="51"/>
-      <c r="E56" s="51"/>
-      <c r="F56" s="52"/>
+      <c r="B56" s="53"/>
+      <c r="C56" s="53"/>
+      <c r="D56" s="53"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="54"/>
       <c r="G56" s="37"/>
       <c r="H56" s="37"/>
       <c r="I56" s="37"/>
@@ -19030,11 +19052,11 @@
       <c r="N56" s="25"/>
     </row>
     <row r="57" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="91" t="s">
-        <v>716</v>
+      <c r="A57" s="92" t="s">
+        <v>701</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>118</v>
@@ -19052,12 +19074,12 @@
       <c r="N57" s="25"/>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="91"/>
+      <c r="A58" s="92"/>
       <c r="B58" s="15" t="s">
-        <v>717</v>
+        <v>702</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -19072,12 +19094,12 @@
       <c r="N58" s="25"/>
     </row>
     <row r="59" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="91"/>
+      <c r="A59" s="92"/>
       <c r="B59" s="15" t="s">
-        <v>718</v>
+        <v>703</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -19092,12 +19114,12 @@
       <c r="N59" s="25"/>
     </row>
     <row r="60" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="91"/>
+      <c r="A60" s="92"/>
       <c r="B60" s="15" t="s">
-        <v>719</v>
+        <v>704</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -19112,12 +19134,12 @@
       <c r="N60" s="25"/>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="91"/>
+      <c r="A61" s="92"/>
       <c r="B61" s="15" t="s">
-        <v>720</v>
+        <v>705</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -19132,12 +19154,12 @@
       <c r="N61" s="25"/>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="91"/>
+      <c r="A62" s="92"/>
       <c r="B62" s="15" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -19152,12 +19174,12 @@
       <c r="N62" s="25"/>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="91"/>
+      <c r="A63" s="92"/>
       <c r="B63" s="15" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -19172,12 +19194,12 @@
       <c r="N63" s="25"/>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="91"/>
+      <c r="A64" s="92"/>
       <c r="B64" s="15" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -19192,12 +19214,12 @@
       <c r="N64" s="25"/>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="91"/>
+      <c r="A65" s="92"/>
       <c r="B65" s="15" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -19212,14 +19234,14 @@
       <c r="N65" s="25"/>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="93" t="s">
+      <c r="A66" s="96" t="s">
         <v>114</v>
       </c>
-      <c r="B66" s="54"/>
-      <c r="C66" s="54"/>
-      <c r="D66" s="54"/>
-      <c r="E66" s="54"/>
-      <c r="F66" s="55"/>
+      <c r="B66" s="87"/>
+      <c r="C66" s="87"/>
+      <c r="D66" s="87"/>
+      <c r="E66" s="87"/>
+      <c r="F66" s="88"/>
       <c r="G66" s="46"/>
       <c r="H66" s="46"/>
       <c r="I66" s="46"/>
@@ -19230,14 +19252,14 @@
       <c r="N66" s="27"/>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="56" t="s">
+      <c r="A67" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="B67" s="57"/>
-      <c r="C67" s="57"/>
-      <c r="D67" s="57"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="58"/>
+      <c r="B67" s="90"/>
+      <c r="C67" s="90"/>
+      <c r="D67" s="90"/>
+      <c r="E67" s="90"/>
+      <c r="F67" s="91"/>
       <c r="G67" s="47"/>
       <c r="H67" s="47"/>
       <c r="I67" s="47"/>
@@ -19265,6 +19287,17 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A8:A30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A32:A39"/>
+    <mergeCell ref="A41:A49"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="A57:A65"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
@@ -19280,17 +19313,6 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="A67:F67"/>
-    <mergeCell ref="A51:A55"/>
-    <mergeCell ref="A57:A65"/>
-    <mergeCell ref="A8:A30"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A32:A39"/>
-    <mergeCell ref="A41:A49"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21775,20 +21797,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="80"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30"/>
@@ -21804,13 +21826,13 @@
       <c r="K3" s="30"/>
       <c r="L3" s="30"/>
       <c r="M3" s="31" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="N3" s="49"/>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M4" s="36" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="N4" s="49"/>
     </row>
@@ -21819,74 +21841,74 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88" t="s">
-        <v>414</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>624</v>
-      </c>
-      <c r="C6" s="83" t="s">
-        <v>625</v>
-      </c>
-      <c r="D6" s="83" t="s">
-        <v>626</v>
-      </c>
-      <c r="E6" s="83" t="s">
-        <v>627</v>
-      </c>
-      <c r="F6" s="78" t="s">
-        <v>628</v>
-      </c>
-      <c r="G6" s="78" t="s">
-        <v>578</v>
-      </c>
-      <c r="H6" s="78" t="s">
-        <v>582</v>
-      </c>
-      <c r="I6" s="78" t="s">
-        <v>588</v>
-      </c>
-      <c r="J6" s="78" t="s">
-        <v>589</v>
-      </c>
-      <c r="K6" s="78" t="s">
-        <v>590</v>
-      </c>
-      <c r="L6" s="78" t="s">
-        <v>608</v>
-      </c>
-      <c r="M6" s="78" t="s">
-        <v>629</v>
-      </c>
-      <c r="N6" s="81" t="s">
-        <v>630</v>
+      <c r="A6" s="64" t="s">
+        <v>412</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>616</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>617</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>618</v>
+      </c>
+      <c r="E6" s="59" t="s">
+        <v>619</v>
+      </c>
+      <c r="F6" s="55" t="s">
+        <v>620</v>
+      </c>
+      <c r="G6" s="55" t="s">
+        <v>575</v>
+      </c>
+      <c r="H6" s="55" t="s">
+        <v>579</v>
+      </c>
+      <c r="I6" s="55" t="s">
+        <v>585</v>
+      </c>
+      <c r="J6" s="55" t="s">
+        <v>586</v>
+      </c>
+      <c r="K6" s="55" t="s">
+        <v>587</v>
+      </c>
+      <c r="L6" s="55" t="s">
+        <v>600</v>
+      </c>
+      <c r="M6" s="55" t="s">
+        <v>621</v>
+      </c>
+      <c r="N6" s="71" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="89"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="84"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="79"/>
-      <c r="K7" s="79"/>
-      <c r="L7" s="79"/>
-      <c r="M7" s="79"/>
-      <c r="N7" s="82"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="72"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="94" t="s">
-        <v>724</v>
+      <c r="A8" s="95" t="s">
+        <v>709</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>174</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -21901,12 +21923,12 @@
       <c r="N8" s="26"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="90"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="13" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -21921,7 +21943,7 @@
       <c r="N9" s="25"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="90"/>
+      <c r="A10" s="93"/>
       <c r="B10" s="11" t="s">
         <v>184</v>
       </c>
@@ -21941,12 +21963,12 @@
       <c r="N10" s="25"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="90"/>
+      <c r="A11" s="93"/>
       <c r="B11" s="11" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
@@ -21961,12 +21983,12 @@
       <c r="N11" s="25"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="90"/>
+      <c r="A12" s="93"/>
       <c r="B12" s="11" t="s">
         <v>188</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
@@ -21981,9 +22003,9 @@
       <c r="N12" s="25"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="90"/>
+      <c r="A13" s="93"/>
       <c r="B13" s="11" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>181</v>
@@ -22001,14 +22023,14 @@
       <c r="N13" s="25"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="90" t="s">
-        <v>725</v>
+      <c r="A14" s="93" t="s">
+        <v>710</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -22023,12 +22045,12 @@
       <c r="N14" s="25"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="90"/>
+      <c r="A15" s="93"/>
       <c r="B15" s="11" t="s">
         <v>192</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -22043,12 +22065,12 @@
       <c r="N15" s="25"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="90"/>
+      <c r="A16" s="93"/>
       <c r="B16" s="11" t="s">
         <v>179</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -22063,7 +22085,7 @@
       <c r="N16" s="25"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="90"/>
+      <c r="A17" s="93"/>
       <c r="B17" s="11" t="s">
         <v>175</v>
       </c>
@@ -22084,13 +22106,13 @@
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>722</v>
+        <v>707</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -22105,14 +22127,14 @@
       <c r="N18" s="25"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="93" t="s">
+      <c r="A19" s="96" t="s">
         <v>114</v>
       </c>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="55"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="88"/>
       <c r="G19" s="46"/>
       <c r="H19" s="46"/>
       <c r="I19" s="46"/>
@@ -22123,14 +22145,14 @@
       <c r="N19" s="27"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="57"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="58"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="91"/>
       <c r="G20" s="47"/>
       <c r="H20" s="47"/>
       <c r="I20" s="47"/>
@@ -22174,6 +22196,11 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
@@ -22188,11 +22215,6 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:I7"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
